--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37B938A-AF0E-4719-86FA-3FB5484BB01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB30DD9-90BA-4863-988D-946263078CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="1006">
   <si>
     <t>name</t>
   </si>
@@ -1825,6 +1825,1230 @@
   </si>
   <si>
     <t>An incremental update refining C++20 features and improving compile-time and library ergonomics.</t>
+  </si>
+  <si>
+    <t>R 4.6.0</t>
+  </si>
+  <si>
+    <t>2026‑04‑24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2029‑04‑24</t>
+  </si>
+  <si>
+    <t>Improved performance, updated base packages, memory optimizations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Legacy package compatibility issues, slow single‑thread operations</t>
+  </si>
+  <si>
+    <t>R Core Team</t>
+  </si>
+  <si>
+    <t>Latest stable R release with performance improvements and updated statistical capabilities.</t>
+  </si>
+  <si>
+    <t>R 4.4.0</t>
+  </si>
+  <si>
+    <t>2024‑04‑24</t>
+  </si>
+  <si>
+    <t>2027‑04‑24</t>
+  </si>
+  <si>
+    <t>Faster matrix ops, updated compiler</t>
+  </si>
+  <si>
+    <t>Limited multicore scaling</t>
+  </si>
+  <si>
+    <t>Major release improving performance and developer experience</t>
+  </si>
+  <si>
+    <t>R 4.4.3</t>
+  </si>
+  <si>
+    <t>2025‑02‑28</t>
+  </si>
+  <si>
+    <t>2028‑02‑28</t>
+  </si>
+  <si>
+    <t>Bug fixes, improved OS support</t>
+  </si>
+  <si>
+    <t>Some CRAN package inconsistencies</t>
+  </si>
+  <si>
+    <t>Stable maintenance release widely used in enterprise</t>
+  </si>
+  <si>
+    <t>R 4.5.0</t>
+  </si>
+  <si>
+    <t>2025‑04‑11</t>
+  </si>
+  <si>
+    <t>2028‑04‑11</t>
+  </si>
+  <si>
+    <t>New base features, improved graphics engine</t>
+  </si>
+  <si>
+    <t>Regressions in niche statistical functions</t>
+  </si>
+  <si>
+    <t>Major update with enhancements to graphics and modeling</t>
+  </si>
+  <si>
+    <t>R 4.5.1</t>
+  </si>
+  <si>
+    <t>2025‑06‑13</t>
+  </si>
+  <si>
+    <t>2028‑06‑13</t>
+  </si>
+  <si>
+    <t>Minor enhancements, updated base functions</t>
+  </si>
+  <si>
+    <t>Performance limits on large datasets</t>
+  </si>
+  <si>
+    <t>Patch release improving reliability and stability</t>
+  </si>
+  <si>
+    <t>R 4.5.3</t>
+  </si>
+  <si>
+    <t>2026‑03‑11</t>
+  </si>
+  <si>
+    <t>2029‑03‑11</t>
+  </si>
+  <si>
+    <t>Bug fixes, stability improvements</t>
+  </si>
+  <si>
+    <t>Minor CRAN inconsistencies</t>
+  </si>
+  <si>
+    <t>Maintenance release improving package compatibility</t>
+  </si>
+  <si>
+    <t>MATLAB R2024a</t>
+  </si>
+  <si>
+    <t>2024‑03‑20</t>
+  </si>
+  <si>
+    <t>2027‑03‑20</t>
+  </si>
+  <si>
+    <t>Performance improvements, updated toolboxes</t>
+  </si>
+  <si>
+    <t>Limited GPU support for some toolboxes</t>
+  </si>
+  <si>
+    <t>MathWorks</t>
+  </si>
+  <si>
+    <t>88.50</t>
+  </si>
+  <si>
+    <t>84.20</t>
+  </si>
+  <si>
+    <t>79.75</t>
+  </si>
+  <si>
+    <t>78.40</t>
+  </si>
+  <si>
+    <t>87.10</t>
+  </si>
+  <si>
+    <t>82.60</t>
+  </si>
+  <si>
+    <t>76.30</t>
+  </si>
+  <si>
+    <t>83.20</t>
+  </si>
+  <si>
+    <t>89.40</t>
+  </si>
+  <si>
+    <t>85.10</t>
+  </si>
+  <si>
+    <t>81.25</t>
+  </si>
+  <si>
+    <t>82.75</t>
+  </si>
+  <si>
+    <t>88.90</t>
+  </si>
+  <si>
+    <t>84.70</t>
+  </si>
+  <si>
+    <t>80.10</t>
+  </si>
+  <si>
+    <t>84.10</t>
+  </si>
+  <si>
+    <t>90.20</t>
+  </si>
+  <si>
+    <t>86.40</t>
+  </si>
+  <si>
+    <t>82.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 89.50</t>
+  </si>
+  <si>
+    <t>94.80</t>
+  </si>
+  <si>
+    <t>91.60</t>
+  </si>
+  <si>
+    <t>88.30</t>
+  </si>
+  <si>
+    <t>96.40</t>
+  </si>
+  <si>
+    <t>89.50</t>
+  </si>
+  <si>
+    <t>MATLAB R2024b</t>
+  </si>
+  <si>
+    <t>2024‑09‑11</t>
+  </si>
+  <si>
+    <t>2027‑09‑11</t>
+  </si>
+  <si>
+    <t>Bug fixes, toolbox updates</t>
+  </si>
+  <si>
+    <t>Stable release widely used in engineering, data analysis, and research environments</t>
+  </si>
+  <si>
+    <t>Minor compatibility issues with older projects</t>
+  </si>
+  <si>
+    <t>91.10</t>
+  </si>
+  <si>
+    <t>95.20</t>
+  </si>
+  <si>
+    <t>96.80</t>
+  </si>
+  <si>
+    <t>90.30</t>
+  </si>
+  <si>
+    <t>Autumn release focused on stability and enhanced toolbox support</t>
+  </si>
+  <si>
+    <t>MATLAB R2025a</t>
+  </si>
+  <si>
+    <t>2025‑05‑14</t>
+  </si>
+  <si>
+    <t>2028‑05‑14</t>
+  </si>
+  <si>
+    <t>New desktop layout, customizable sidebars, theme support</t>
+  </si>
+  <si>
+    <t>Layout incompatibility with older MATLAB versions</t>
+  </si>
+  <si>
+    <t>92.40</t>
+  </si>
+  <si>
+    <t>96.10</t>
+  </si>
+  <si>
+    <t>97.20</t>
+  </si>
+  <si>
+    <t>91.80</t>
+  </si>
+  <si>
+    <t>Major UI update improving user experience and workflow customization</t>
+  </si>
+  <si>
+    <t>MATLAB R2025b</t>
+  </si>
+  <si>
+    <t>2025‑09‑17</t>
+  </si>
+  <si>
+    <t>2028‑09‑17</t>
+  </si>
+  <si>
+    <t>Performance improvements, faster getframe function</t>
+  </si>
+  <si>
+    <t>Video capture limitations on older hardware</t>
+  </si>
+  <si>
+    <t>92.90</t>
+  </si>
+  <si>
+    <t>96.50</t>
+  </si>
+  <si>
+    <t>97.60</t>
+  </si>
+  <si>
+    <t>92.30</t>
+  </si>
+  <si>
+    <t>Performance‑focused release with graphics and rendering optimizations</t>
+  </si>
+  <si>
+    <t>MATLAB R2026a</t>
+  </si>
+  <si>
+    <t>2026‑04‑15</t>
+  </si>
+  <si>
+    <t>2029‑04‑15</t>
+  </si>
+  <si>
+    <t>MATLAB Drive file sharing, custom Java installation, multilevel lists in Live Editor</t>
+  </si>
+  <si>
+    <t>Java dependency differences across platforms</t>
+  </si>
+  <si>
+    <t>94.30</t>
+  </si>
+  <si>
+    <t>97.80</t>
+  </si>
+  <si>
+    <t>98.40</t>
+  </si>
+  <si>
+    <t>93.90</t>
+  </si>
+  <si>
+    <t>Latest release introducing collaboration features and enhanced Live Editor capabilities</t>
+  </si>
+  <si>
+    <t>Perl 5.38.0</t>
+  </si>
+  <si>
+    <t>2023‑07‑03</t>
+  </si>
+  <si>
+    <t>2025‑08‑03</t>
+  </si>
+  <si>
+    <t>New class feature, Unicode 15, improved flow‑control</t>
+  </si>
+  <si>
+    <t>Deprecated smartmatch &amp; switch, limited modernization</t>
+  </si>
+  <si>
+    <t>Larry Wall</t>
+  </si>
+  <si>
+    <t>74.20</t>
+  </si>
+  <si>
+    <t>82.50</t>
+  </si>
+  <si>
+    <t>70.40</t>
+  </si>
+  <si>
+    <t>68.30</t>
+  </si>
+  <si>
+    <t>Introduced modern class syntax and Unicode 15 support, improving language consistency.</t>
+  </si>
+  <si>
+    <t>Perl 5.40.0</t>
+  </si>
+  <si>
+    <t>2024‑06‑09</t>
+  </si>
+  <si>
+    <t>2027‑06‑09</t>
+  </si>
+  <si>
+    <t>New __CLASS__ keyword, new builtin functions, improved try/catch</t>
+  </si>
+  <si>
+    <t>Some experimental features still unstable</t>
+  </si>
+  <si>
+    <t>78.60</t>
+  </si>
+  <si>
+    <t>85.40</t>
+  </si>
+  <si>
+    <t>73.90</t>
+  </si>
+  <si>
+    <t>72.10</t>
+  </si>
+  <si>
+    <t>A stability‑focused release adding new keywords, improved exception handling, and security fixes.</t>
+  </si>
+  <si>
+    <t>Perl 5.40.2</t>
+  </si>
+  <si>
+    <t>2025‑04‑13</t>
+  </si>
+  <si>
+    <t>2028‑04‑13</t>
+  </si>
+  <si>
+    <t>Security fixes, maintenance updates</t>
+  </si>
+  <si>
+    <t>No major unresolved issues; maintenance‑only</t>
+  </si>
+  <si>
+    <t>79.10</t>
+  </si>
+  <si>
+    <t>86.20</t>
+  </si>
+  <si>
+    <t>74.80</t>
+  </si>
+  <si>
+    <t>72.90</t>
+  </si>
+  <si>
+    <t>Maintenance release delivering security patches and incremental improvements.</t>
+  </si>
+  <si>
+    <t>Perl 5.40.3</t>
+  </si>
+  <si>
+    <t>Security fixes</t>
+  </si>
+  <si>
+    <t>Minor legacy module compatibility issues</t>
+  </si>
+  <si>
+    <t>79.40</t>
+  </si>
+  <si>
+    <t>86.70</t>
+  </si>
+  <si>
+    <t>75.10</t>
+  </si>
+  <si>
+    <t>73.40</t>
+  </si>
+  <si>
+    <t>Security‑focused update improving long‑term stability of the 5.40 branch.</t>
+  </si>
+  <si>
+    <t>Perl 5.42.0</t>
+  </si>
+  <si>
+    <t>2025‑07‑03</t>
+  </si>
+  <si>
+    <t>2029‑07‑03</t>
+  </si>
+  <si>
+    <t>New :writer attribute, lexical methods, new operators, Unicode 16</t>
+  </si>
+  <si>
+    <t>Some experimental features still evolving</t>
+  </si>
+  <si>
+    <t>82.30</t>
+  </si>
+  <si>
+    <t>76.80</t>
+  </si>
+  <si>
+    <t>Major feature release introducing lexical methods, new operators, and Unicode 16 support.</t>
+  </si>
+  <si>
+    <t>Perl 5.42.2</t>
+  </si>
+  <si>
+    <t>2026‑03‑29</t>
+  </si>
+  <si>
+    <t>2029‑03‑29</t>
+  </si>
+  <si>
+    <t>Maintenance fixes, security updates</t>
+  </si>
+  <si>
+    <t>No major unresolved issues</t>
+  </si>
+  <si>
+    <t>83.10</t>
+  </si>
+  <si>
+    <t>79.20</t>
+  </si>
+  <si>
+    <t>77.50</t>
+  </si>
+  <si>
+    <t>Latest stable maintenance release with security and reliability improvements.</t>
+  </si>
+  <si>
+    <t>Spring Boot 3.3.0</t>
+  </si>
+  <si>
+    <t>2024‑05‑23</t>
+  </si>
+  <si>
+    <t>2025‑06‑30</t>
+  </si>
+  <si>
+    <t>Improved native image support, updated dependencies</t>
+  </si>
+  <si>
+    <t>Limited compatibility with older Spring 2.x apps</t>
+  </si>
+  <si>
+    <t>VMware / Spring Team</t>
+  </si>
+  <si>
+    <t>88.40</t>
+  </si>
+  <si>
+    <t>92.10</t>
+  </si>
+  <si>
+    <t>87.20</t>
+  </si>
+  <si>
+    <t>Modern release focused on performance, native image support, and updated Jakarta EE 10 baseline.</t>
+  </si>
+  <si>
+    <t>Spring Boot 3.4.0</t>
+  </si>
+  <si>
+    <t>2024‑11‑21</t>
+  </si>
+  <si>
+    <t>2025‑12‑31</t>
+  </si>
+  <si>
+    <t>Dependency upgrades, improved actuator endpoints</t>
+  </si>
+  <si>
+    <t>Short support window, minor migration issues</t>
+  </si>
+  <si>
+    <t>89.10</t>
+  </si>
+  <si>
+    <t>92.80</t>
+  </si>
+  <si>
+    <t>91.00</t>
+  </si>
+  <si>
+    <t>Stability‑focused release improving observability and dependency alignment.</t>
+  </si>
+  <si>
+    <t>Spring Boot 3.5.0</t>
+  </si>
+  <si>
+    <t>2025‑05‑22</t>
+  </si>
+  <si>
+    <t>2026‑06‑30</t>
+  </si>
+  <si>
+    <t>Enhanced AOT support, improved Docker image building</t>
+  </si>
+  <si>
+    <t>Some native image edge‑cases remain</t>
+  </si>
+  <si>
+    <t>93.40</t>
+  </si>
+  <si>
+    <t>89.30</t>
+  </si>
+  <si>
+    <t>Release improving AOT compilation, containerization, and cloud‑native workflows.</t>
+  </si>
+  <si>
+    <t>Spring Boot 4.0.0</t>
+  </si>
+  <si>
+    <t>2025‑11‑20</t>
+  </si>
+  <si>
+    <t>2026‑12‑31</t>
+  </si>
+  <si>
+    <t>Java 17+ baseline, improved HTTP client, updated Spring Framework 7</t>
+  </si>
+  <si>
+    <t>Migration complexity for older 2.x/3.x apps</t>
+  </si>
+  <si>
+    <t>95.10</t>
+  </si>
+  <si>
+    <t>94.20</t>
+  </si>
+  <si>
+    <t>91.50</t>
+  </si>
+  <si>
+    <t>Major release introducing new Java baselines, improved performance, and modernized APIs.</t>
+  </si>
+  <si>
+    <t>Spring Boot 4.1.0‑RC1</t>
+  </si>
+  <si>
+    <t>2026‑04‑23</t>
+  </si>
+  <si>
+    <t>2027‑06‑30</t>
+  </si>
+  <si>
+    <t>Elasticsearch support updates, Redis listener improvements, OpenTelemetry enhancements</t>
+  </si>
+  <si>
+    <t>Pre‑release stability issues</t>
+  </si>
+  <si>
+    <t>95.80</t>
+  </si>
+  <si>
+    <t>94.90</t>
+  </si>
+  <si>
+    <t>92.70</t>
+  </si>
+  <si>
+    <t>Feature‑rich release candidate adding observability, messaging, and cloud‑native improvements.</t>
+  </si>
+  <si>
+    <t>Spring Cloud 2023.0 (Leyton)</t>
+  </si>
+  <si>
+    <t>2023‑12‑01</t>
+  </si>
+  <si>
+    <t>2025‑06‑24</t>
+  </si>
+  <si>
+    <t>Gateway 4.1.x updates, Config 4.1.x, OpenFeign 4.1.x</t>
+  </si>
+  <si>
+    <t>Deprecated artifacts, migration warnings</t>
+  </si>
+  <si>
+    <t>Spring Team</t>
+  </si>
+  <si>
+    <t>88.10</t>
+  </si>
+  <si>
+    <t>84.50</t>
+  </si>
+  <si>
+    <t>Stable enterprise release train widely used for microservice architectures.</t>
+  </si>
+  <si>
+    <t>Spring Cloud 2024.0 (Moorgate)</t>
+  </si>
+  <si>
+    <t>2024‑12‑03</t>
+  </si>
+  <si>
+    <t>2026‑01‑01</t>
+  </si>
+  <si>
+    <t>Dependency alignment with Spring Boot 3.4.x, Gateway 4.1.6 updates</t>
+  </si>
+  <si>
+    <t>Requires Spring Framework 6.1.15+ for some modules</t>
+  </si>
+  <si>
+    <t>91.40</t>
+  </si>
+  <si>
+    <t>Modernized release improving compatibility, observability, and dependency consistency.</t>
+  </si>
+  <si>
+    <t>Spring Cloud 2025.0</t>
+  </si>
+  <si>
+    <t>2025‑05‑29</t>
+  </si>
+  <si>
+    <t>Major Gateway module renaming, new property prefix migration, updated Kubernetes/Contract/Stream</t>
+  </si>
+  <si>
+    <t>Migration complexity due to renamed modules</t>
+  </si>
+  <si>
+    <t>93.20</t>
+  </si>
+  <si>
+    <t>88.70</t>
+  </si>
+  <si>
+    <t>Large modernization release improving clarity, naming, and cloud‑native alignment.</t>
+  </si>
+  <si>
+    <t>Spring Cloud 2025.1 (Oakwood)</t>
+  </si>
+  <si>
+    <t>2025‑12‑17</t>
+  </si>
+  <si>
+    <t>2027‑12‑31</t>
+  </si>
+  <si>
+    <t>Updated Gateway, Config, OpenFeign, Stream; dependency upgrades; cleanup of deprecated modules</t>
+  </si>
+  <si>
+    <t>Some deprecated artifacts still require migration</t>
+  </si>
+  <si>
+    <t>94.60</t>
+  </si>
+  <si>
+    <t>90.10</t>
+  </si>
+  <si>
+    <t>Latest stable release train, recommended for new microservice deployments.</t>
+  </si>
+  <si>
+    <t>Quarkus 3.6.0</t>
+  </si>
+  <si>
+    <t>2023‑11‑29</t>
+  </si>
+  <si>
+    <t>2024‑11‑29</t>
+  </si>
+  <si>
+    <t>SSE improvements, OIDC/security enhancements</t>
+  </si>
+  <si>
+    <t>Some legacy extensions still unstable</t>
+  </si>
+  <si>
+    <t>Red Hat</t>
+  </si>
+  <si>
+    <t>82.40</t>
+  </si>
+  <si>
+    <t>80.30</t>
+  </si>
+  <si>
+    <t>78.20</t>
+  </si>
+  <si>
+    <t>Stability‑focused release improving security, SSE, and reactive components.</t>
+  </si>
+  <si>
+    <t>Quarkus 3.7.0</t>
+  </si>
+  <si>
+    <t>2024‑01‑31</t>
+  </si>
+  <si>
+    <t>2025‑01‑31</t>
+  </si>
+  <si>
+    <t>Java 17 baseline, Hibernate ORM 6.4, Micrometer @MeterTag</t>
+  </si>
+  <si>
+    <t>Migration complexity from 3.2 LTS</t>
+  </si>
+  <si>
+    <t>85.60</t>
+  </si>
+  <si>
+    <t>83.90</t>
+  </si>
+  <si>
+    <t>81.70</t>
+  </si>
+  <si>
+    <t>Major modernization release introducing Java 17 baseline and updated Hibernate stack.</t>
+  </si>
+  <si>
+    <t>Quarkus 3.8.1 (LTS)</t>
+  </si>
+  <si>
+    <t>2024‑02‑28</t>
+  </si>
+  <si>
+    <t>Security fixes, CVE patches, improved Quarkus CXF</t>
+  </si>
+  <si>
+    <t>No major issues; maintenance‑focused</t>
+  </si>
+  <si>
+    <t>84.90</t>
+  </si>
+  <si>
+    <t>LTS release with stability, security fixes, and improved native image support.</t>
+  </si>
+  <si>
+    <t>Quarkus 3.15.2 (LTS)</t>
+  </si>
+  <si>
+    <t>2024‑11‑01</t>
+  </si>
+  <si>
+    <t>2025‑11‑01</t>
+  </si>
+  <si>
+    <t>Updated extensions, improved Kubernetes integration</t>
+  </si>
+  <si>
+    <t>Some extensions lag behind new Java versions</t>
+  </si>
+  <si>
+    <t>89.70</t>
+  </si>
+  <si>
+    <t>93.10</t>
+  </si>
+  <si>
+    <t>87.80</t>
+  </si>
+  <si>
+    <t>LTS release improving cloud‑native integration and extension stability.</t>
+  </si>
+  <si>
+    <t>Quarkus 3.33.1 (LTS)</t>
+  </si>
+  <si>
+    <t>2026‑03‑01</t>
+  </si>
+  <si>
+    <t>2027‑03‑01</t>
+  </si>
+  <si>
+    <t>Updated GraalVM/Mandrel support, performance improvements</t>
+  </si>
+  <si>
+    <t>91.20</t>
+  </si>
+  <si>
+    <t>94.40</t>
+  </si>
+  <si>
+    <t>89.90</t>
+  </si>
+  <si>
+    <t>Latest LTS release with enhanced native image tooling and performance upgrades.</t>
+  </si>
+  <si>
+    <t>Micronaut 1.0</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>Ahead-of-time DI, no reflection, ultra-fast startup, minimal memory footprint</t>
+  </si>
+  <si>
+    <t>Limited ecosystem, fewer integrations, early-stage documentation</t>
+  </si>
+  <si>
+    <t>OCI (Object Computing, Inc.)</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> First stable release introducing AOT dependency injection and compile-time bean processing.</t>
+  </si>
+  <si>
+    <t>Micronaut 2.0</t>
+  </si>
+  <si>
+    <t>2020-07-28</t>
+  </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>HTTP/2, GraalVM improvements, Micronaut Launch, better cloud support
+unsolved_problems: Limited enterprise adoption, fewer integrations than Spring</t>
+  </si>
+  <si>
+    <t>OCI</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>Major upgrade with improved cloud-native capabilities and GraalVM optimizations.</t>
+  </si>
+  <si>
+    <t>Micronaut 3.0</t>
+  </si>
+  <si>
+    <t>2021-08-24</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>Java 17 support, Micronaut Data improvements, AOT enhancements, better reactive support</t>
+  </si>
+  <si>
+    <t>Smaller ecosystem compared to Spring Boot</t>
+  </si>
+  <si>
+    <t>Introduced modern Java support and improved developer experience with Micronaut Data.</t>
+  </si>
+  <si>
+    <t>Micronaut 4.0</t>
+  </si>
+  <si>
+    <t>2023-07-25</t>
+  </si>
+  <si>
+    <t>Java 21 support, Jakarta EE namespace migration, improved AOT, faster startup</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>Migration complexity for older apps</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>Major modernization release aligned with Java 21 and Jakarta EE standards.</t>
+  </si>
+  <si>
+    <t>Micronaut 4.3</t>
+  </si>
+  <si>
+    <t>2027-12-31</t>
+  </si>
+  <si>
+    <t>Enhanced Micronaut Data, improved cloud modules, performance boosts</t>
+  </si>
+  <si>
+    <t>Still niche compared to Spring Boot</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>Incremental improvements with focus on performance and cloud-native integrations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jakarta EE 8</t>
+  </si>
+  <si>
+    <t>2019-09-10</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>First release after transition from Java EE; identical APIs to Java EE 8 but under Eclipse Foundation governance</t>
+  </si>
+  <si>
+    <t>No namespace change yet; limited innovation; migration uncertainty</t>
+  </si>
+  <si>
+    <t>Eclipse Foundation</t>
+  </si>
+  <si>
+    <t>Transitional release ensuring compatibility with Java EE 8 while moving the platform to open governance.</t>
+  </si>
+  <si>
+    <t>Jakarta EE 9</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>Major namespace change from javax.* to jakarta.*; platform cleanup; removal of deprecated APIs</t>
+  </si>
+  <si>
+    <t>Breaking changes for all existing applications; slow industry migration</t>
+  </si>
+  <si>
+    <t>Landmark release introducing the new jakarta.* namespace, enabling future innovation.</t>
+  </si>
+  <si>
+    <t>Jakarta EE 9.1</t>
+  </si>
+  <si>
+    <t>2021-05-25</t>
+  </si>
+  <si>
+    <t>Java 11 support, improved compatibility, updated TCKs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Still limited adoption; ecosystem catching up</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>Compatibility-focused release enabling modern Java versions and stabilizing the namespace transition.</t>
+  </si>
+  <si>
+    <t>Jakarta EE 10</t>
+  </si>
+  <si>
+    <t>2022-09-22</t>
+  </si>
+  <si>
+    <t>Java 17 support, new Core Profile, modernized APIs, improved CDI, enhanced security</t>
+  </si>
+  <si>
+    <t>Fragmented vendor support; migration from EE 8 still challenging</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>First truly modern Jakarta EE release with new profiles and updated APIs aligned with modern Java.</t>
+  </si>
+  <si>
+    <t>Jakarta EE 11</t>
+  </si>
+  <si>
+    <t>2028-12-31</t>
+  </si>
+  <si>
+    <t>Java 21 support, improved CDI Lite, enhanced RESTful services, better cloud-native alignment</t>
+  </si>
+  <si>
+    <t>Still behind Spring in ecosystem size; slower release cadence</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>Cloud-ready release aligned with Java 21, focusing on performance, modularity, and modern development practices.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 1.0</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2019-06-27</t>
+  </si>
+  <si>
+    <t>Cross-platform support, modular pipeline, unified MVC/Web API, lightweight hosting</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Limited libraries, missing features vs .NET Framework, early ecosystem</t>
+  </si>
+  <si>
+    <t>First cross-platform release, rebuilt from zero for performance and modularity.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 2.0</t>
+  </si>
+  <si>
+    <t>2017-08-14</t>
+  </si>
+  <si>
+    <t>2020-10-01</t>
+  </si>
+  <si>
+    <t>Razor Pages, simplified hosting, .NET Standard 2.0 support
+unsolved_problems: Still maturing, limited enterprise adoption</t>
+  </si>
+  <si>
+    <t>Major usability improvements and broader API compatibility via .NET Standard 2.0.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 3.1</t>
+  </si>
+  <si>
+    <t>2019-12-03</t>
+  </si>
+  <si>
+    <t>Blazor Server, endpoint routing, gRPC support, improved performance</t>
+  </si>
+  <si>
+    <t>No support for .NET Framework; migration friction</t>
+  </si>
+  <si>
+    <t>LTS release introducing Blazor and modernizing the entire web stack.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 5.0</t>
+  </si>
+  <si>
+    <t>2022-05-10</t>
+  </si>
+  <si>
+    <t>Unified .NET platform, improved Blazor WebAssembly, better performance</t>
+  </si>
+  <si>
+    <t>Short support window, not LTS</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> First unified .NET release, bringing ASP.NET Core fully into the new .NET ecosystem.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 6.0</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>Minimal APIs, hot reload, improved Blazor, better performance
+unsolved_problems: Minimal APIs too new for some enterprise teams</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>Landmark LTS release introducing Minimal APIs and major performance boosts.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 7.0</t>
+  </si>
+  <si>
+    <t>2024-05-14</t>
+  </si>
+  <si>
+    <t>Better minimal APIs, improved SignalR, faster JSON, cloud-native improvements</t>
+  </si>
+  <si>
+    <t>Short support cycle</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>High-performance release with major improvements for cloud-native workloads.</t>
+  </si>
+  <si>
+    <t>ASP.NET Core 8.0</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>Blazor United, enhanced AOT, improved minimal APIs, better cloud integration</t>
+  </si>
+  <si>
+    <t>AOT limitations for dynamic workloads</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>Modern LTS release unifying Blazor models and pushing AOT performance further.</t>
+  </si>
+  <si>
+    <t>NancyFX 0.12</t>
+  </si>
+  <si>
+    <t>2012-03-15</t>
+  </si>
+  <si>
+    <t>2014-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Early lightweight routing, simple module-based architecture, self-hosting</t>
+  </si>
+  <si>
+    <t>Limited performance, incomplete middleware ecosystem</t>
+  </si>
+  <si>
+    <t>NancyFX Team</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>Early pre‑1.0 release that introduced the core philosophy: “Super-duper-happy-path” web development.</t>
+  </si>
+  <si>
+    <t>NancyFX 1.0</t>
+  </si>
+  <si>
+    <t>2014-05-15</t>
+  </si>
+  <si>
+    <t>2017-12-31</t>
+  </si>
+  <si>
+    <t>Stable API, improved routing, view engines, authentication modules, better hosting</t>
   </si>
 </sst>
 </file>
@@ -1868,7 +3092,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1891,11 +3115,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1918,6 +3183,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2204,19 +3493,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}">
-  <dimension ref="A1:L370"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L371"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="28.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="28.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.109375" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -2254,7 +3543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -2292,7 +3581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -2330,7 +3619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -2368,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -2406,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
@@ -2444,7 +3733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
@@ -2482,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
@@ -2520,7 +3809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
@@ -2558,7 +3847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2596,7 +3885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>80</v>
       </c>
@@ -2632,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>87</v>
       </c>
@@ -2670,7 +3959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>95</v>
       </c>
@@ -2708,7 +3997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>101</v>
       </c>
@@ -2746,7 +4035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
@@ -2784,7 +4073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>113</v>
       </c>
@@ -2822,7 +4111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>120</v>
       </c>
@@ -2860,7 +4149,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -2898,7 +4187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>133</v>
       </c>
@@ -2936,7 +4225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>140</v>
       </c>
@@ -2974,7 +4263,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>146</v>
       </c>
@@ -3012,7 +4301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>152</v>
       </c>
@@ -3050,7 +4339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>159</v>
       </c>
@@ -3086,7 +4375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>170</v>
       </c>
@@ -3122,7 +4411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>171</v>
       </c>
@@ -3158,7 +4447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>176</v>
       </c>
@@ -3194,7 +4483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>181</v>
       </c>
@@ -3230,7 +4519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>186</v>
       </c>
@@ -3266,7 +4555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>192</v>
       </c>
@@ -3302,7 +4591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>197</v>
       </c>
@@ -3338,7 +4627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>202</v>
       </c>
@@ -3374,7 +4663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>207</v>
       </c>
@@ -3410,7 +4699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>208</v>
       </c>
@@ -3446,7 +4735,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>209</v>
       </c>
@@ -3482,7 +4771,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>221</v>
       </c>
@@ -3518,7 +4807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>226</v>
       </c>
@@ -3554,7 +4843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>231</v>
       </c>
@@ -3590,7 +4879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>236</v>
       </c>
@@ -3626,7 +4915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>243</v>
       </c>
@@ -3662,7 +4951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>249</v>
       </c>
@@ -3698,7 +4987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>254</v>
       </c>
@@ -3736,7 +5025,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>261</v>
       </c>
@@ -3774,7 +5063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>267</v>
       </c>
@@ -3812,7 +5101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>273</v>
       </c>
@@ -3850,7 +5139,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>279</v>
       </c>
@@ -3888,7 +5177,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>284</v>
       </c>
@@ -3926,7 +5215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>289</v>
       </c>
@@ -3964,7 +5253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>295</v>
       </c>
@@ -4002,7 +5291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>301</v>
       </c>
@@ -4038,7 +5327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>307</v>
       </c>
@@ -4074,7 +5363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>312</v>
       </c>
@@ -4110,7 +5399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>318</v>
       </c>
@@ -4146,7 +5435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>321</v>
       </c>
@@ -4182,7 +5471,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>326</v>
       </c>
@@ -4218,7 +5507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>331</v>
       </c>
@@ -4254,7 +5543,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>336</v>
       </c>
@@ -4290,7 +5579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>340</v>
       </c>
@@ -4326,7 +5615,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>346</v>
       </c>
@@ -4362,7 +5651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>351</v>
       </c>
@@ -4398,7 +5687,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>356</v>
       </c>
@@ -4434,7 +5723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>361</v>
       </c>
@@ -4470,7 +5759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>366</v>
       </c>
@@ -4506,7 +5795,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>371</v>
       </c>
@@ -4542,7 +5831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>376</v>
       </c>
@@ -4578,7 +5867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>380</v>
       </c>
@@ -4614,7 +5903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>386</v>
       </c>
@@ -4650,7 +5939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>391</v>
       </c>
@@ -4686,7 +5975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>396</v>
       </c>
@@ -4722,7 +6011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>402</v>
       </c>
@@ -4758,7 +6047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>403</v>
       </c>
@@ -4794,7 +6083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>404</v>
       </c>
@@ -4830,7 +6119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>405</v>
       </c>
@@ -4866,7 +6155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>420</v>
       </c>
@@ -4904,7 +6193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>427</v>
       </c>
@@ -4942,7 +6231,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>433</v>
       </c>
@@ -4980,7 +6269,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>439</v>
       </c>
@@ -5018,7 +6307,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>445</v>
       </c>
@@ -5056,7 +6345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>451</v>
       </c>
@@ -5094,7 +6383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>452</v>
       </c>
@@ -5132,7 +6421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>462</v>
       </c>
@@ -5170,7 +6459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>469</v>
       </c>
@@ -5208,7 +6497,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>475</v>
       </c>
@@ -5246,7 +6535,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>481</v>
       </c>
@@ -5284,7 +6573,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>487</v>
       </c>
@@ -5320,7 +6609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>493</v>
       </c>
@@ -5356,7 +6645,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
         <v>498</v>
       </c>
@@ -5392,7 +6681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
         <v>503</v>
       </c>
@@ -5428,7 +6717,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
         <v>509</v>
       </c>
@@ -5464,7 +6753,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
         <v>515</v>
       </c>
@@ -5500,7 +6789,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
         <v>520</v>
       </c>
@@ -5536,7 +6825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
         <v>525</v>
       </c>
@@ -5572,7 +6861,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>531</v>
       </c>
@@ -5608,7 +6897,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>536</v>
       </c>
@@ -5644,7 +6933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>541</v>
       </c>
@@ -5680,7 +6969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
         <v>545</v>
       </c>
@@ -5716,7 +7005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>552</v>
       </c>
@@ -5752,7 +7041,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
         <v>558</v>
       </c>
@@ -5788,7 +7077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
         <v>563</v>
       </c>
@@ -5824,7 +7113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
         <v>568</v>
       </c>
@@ -5860,7 +7149,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
         <v>573</v>
       </c>
@@ -5896,7 +7185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
         <v>579</v>
       </c>
@@ -5932,7 +7221,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
         <v>584</v>
       </c>
@@ -5968,7 +7257,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
         <v>589</v>
       </c>
@@ -6004,477 +7293,1221 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A104" s="3" t="s">
+    <row r="104" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="13" t="s">
         <v>594</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="14" t="s">
         <v>595</v>
       </c>
-      <c r="C104" s="4"/>
-      <c r="D104" s="5" t="s">
+      <c r="C104" s="14"/>
+      <c r="D104" s="15" t="s">
         <v>596</v>
       </c>
-      <c r="E104" s="5" t="s">
+      <c r="E104" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="F104" s="5" t="s">
+      <c r="F104" s="15" t="s">
         <v>577</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H104" s="4" t="s">
+      <c r="H104" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I104" s="4" t="s">
+      <c r="I104" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="J104" s="4" t="s">
+      <c r="J104" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="K104" s="5" t="s">
+      <c r="K104" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="L104" s="5">
+      <c r="L104" s="15">
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="4"/>
-      <c r="H105" s="4"/>
-      <c r="I105" s="4"/>
-      <c r="J105" s="4"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="5"/>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="5"/>
-      <c r="L108" s="5"/>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="4"/>
-      <c r="H109" s="4"/>
-      <c r="I109" s="4"/>
-      <c r="J109" s="4"/>
-      <c r="K109" s="5"/>
-      <c r="L109" s="5"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="4"/>
-      <c r="H110" s="4"/>
-      <c r="I110" s="4"/>
-      <c r="J110" s="4"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="5"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="4"/>
-      <c r="H111" s="4"/>
-      <c r="I111" s="4"/>
-      <c r="J111" s="4"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="3"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="3"/>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="4"/>
-      <c r="H114" s="4"/>
-      <c r="I114" s="4"/>
-      <c r="J114" s="4"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="3"/>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="4"/>
-      <c r="J115" s="4"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="3"/>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="4"/>
-      <c r="J116" s="4"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="3"/>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="4"/>
-      <c r="J117" s="4"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="3"/>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
-      <c r="J118" s="4"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="3"/>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
-      <c r="J119" s="4"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="3"/>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A120" s="3"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
-      <c r="J120" s="4"/>
-      <c r="K120" s="5"/>
-      <c r="L120" s="3"/>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
-      <c r="J121" s="4"/>
-      <c r="K121" s="5"/>
-      <c r="L121" s="3"/>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
-      <c r="J122" s="4"/>
-      <c r="K122" s="5"/>
-      <c r="L122" s="3"/>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A123" s="3"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
-      <c r="J123" s="4"/>
-      <c r="K123" s="5"/>
-      <c r="L123" s="3"/>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A124" s="3"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
-      <c r="J124" s="4"/>
-      <c r="K124" s="5"/>
-      <c r="L124" s="3"/>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
-      <c r="J125" s="4"/>
-      <c r="K125" s="5"/>
-      <c r="L125" s="3"/>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A126" s="3"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-      <c r="I126" s="4"/>
-      <c r="J126" s="4"/>
-      <c r="K126" s="5"/>
-      <c r="L126" s="3"/>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="4"/>
-      <c r="H127" s="4"/>
-      <c r="I127" s="4"/>
-      <c r="J127" s="4"/>
-      <c r="K127" s="5"/>
-      <c r="L127" s="3"/>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A128" s="3"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="4"/>
-      <c r="J128" s="4"/>
-      <c r="K128" s="5"/>
-      <c r="L128" s="3"/>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A129" s="3"/>
-      <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="4"/>
-      <c r="H129" s="4"/>
-      <c r="I129" s="4"/>
-      <c r="J129" s="4"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="3"/>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A130" s="3"/>
-      <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="4"/>
-      <c r="H130" s="4"/>
-      <c r="I130" s="4"/>
-      <c r="J130" s="4"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="3"/>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A131" s="3"/>
-      <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="4"/>
-      <c r="H131" s="4"/>
-      <c r="I131" s="4"/>
-      <c r="J131" s="4"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="3"/>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
-      <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="4"/>
-      <c r="H132" s="4"/>
-      <c r="I132" s="4"/>
-      <c r="J132" s="4"/>
-      <c r="K132" s="5"/>
-      <c r="L132" s="3"/>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A133" s="3"/>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="5"/>
-      <c r="E133" s="5"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="3"/>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A134" s="3"/>
-      <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
-      <c r="D134" s="5"/>
-      <c r="E134" s="5"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="3"/>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A135" s="3"/>
-      <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="4"/>
-      <c r="H135" s="4"/>
-      <c r="I135" s="4"/>
-      <c r="J135" s="4"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="3"/>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>607</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>608</v>
+      </c>
+      <c r="D105" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="F105" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G105" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H105" s="11" t="s">
+        <v>642</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="K105" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="L105" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A106" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="I106" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="K106" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="L106" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A107" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="F107" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="K107" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="L107" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I108" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="K108" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="L108" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A109" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>631</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="F109" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="K109" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="L109" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A110" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="I110" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="J110" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="K110" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="L110" s="5">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A111" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="L111" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A112" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="I112" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="L112" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A113" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="K113" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="L113" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>692</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="I114" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="K114" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="L114" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A115" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="K115" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="L115" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A116" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="I116" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="J116" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="K116" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="L116" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A117" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="L117" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A118" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="I118" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="K118" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="L118" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A119" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>740</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="K119" s="5" t="s">
+        <v>746</v>
+      </c>
+      <c r="L119" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A120" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>750</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>751</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I120" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="J120" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="K120" s="5" t="s">
+        <v>754</v>
+      </c>
+      <c r="L120" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>759</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="K121" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="L121" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A122" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="I122" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="J122" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="K122" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="L122" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A123" s="3" t="s">
+        <v>774</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="K123" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="L123" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A124" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="I124" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="J124" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="K124" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="L124" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A125" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="L125" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A126" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>803</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="I126" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="J126" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="K126" s="5" t="s">
+        <v>808</v>
+      </c>
+      <c r="L126" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A127" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="K127" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="L127" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A128" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>821</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="I128" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="J128" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="K128" s="5" t="s">
+        <v>824</v>
+      </c>
+      <c r="L128" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>827</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="K129" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="L129" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A130" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="I130" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="J130" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="K130" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="L130" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A131" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="K131" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="L131" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B132" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="I132" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="J132" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="K132" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="L132" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A133" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="K133" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="L133" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A134" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="I134" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="J134" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="K134" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="L134" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A135" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>787</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>878</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="K135" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="L135" s="3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="198" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -6488,263 +8521,697 @@
       <c r="K136" s="5"/>
       <c r="L136" s="3"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A137" s="3"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="5"/>
-      <c r="E137" s="5"/>
-      <c r="F137" s="5"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="3"/>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A138" s="3"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="5"/>
+    <row r="137" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A137" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="K137" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="L137" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="135" x14ac:dyDescent="0.25">
+      <c r="A138" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>896</v>
+      </c>
       <c r="E138" s="5"/>
-      <c r="F138" s="5"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="3"/>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A139" s="3"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="5"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="3"/>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A140" s="3"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="5"/>
-      <c r="E140" s="5"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="3"/>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A141" s="3"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="5"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="3"/>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="3"/>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A143" s="3"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="5"/>
-      <c r="E143" s="5"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="5"/>
-      <c r="L143" s="3"/>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A144" s="3"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="5"/>
-      <c r="E144" s="5"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
-      <c r="K144" s="5"/>
-      <c r="L144" s="3"/>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A145" s="3"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="5"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="3"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A146" s="3"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="5"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="3"/>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A147" s="3"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="5"/>
-      <c r="E147" s="5"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="4"/>
-      <c r="H147" s="4"/>
-      <c r="I147" s="4"/>
-      <c r="J147" s="4"/>
-      <c r="K147" s="5"/>
-      <c r="L147" s="3"/>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A148" s="3"/>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="5"/>
+      <c r="F138" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="I138" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J138" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="K138" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="L138" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A139" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="B139" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>904</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="G139" s="5">
+        <v>75</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K139" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="L139" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A140" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I140" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J140" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="K140" s="5" t="s">
+        <v>914</v>
+      </c>
+      <c r="L140" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A141" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K141" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="L141" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>928</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="J142" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K142" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="L142" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A143" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>935</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J143" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="K143" s="5" t="s">
+        <v>936</v>
+      </c>
+      <c r="L143" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>939</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I144" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J144" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K144" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="L144" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A145" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="K145" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="L145" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A146" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C146" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>951</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>929</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="I146" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J146" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K146" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="L146" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A147" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>958</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>959</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J147" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K147" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="L147" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A148" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>964</v>
+      </c>
       <c r="E148" s="5"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="5"/>
-      <c r="L148" s="3"/>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A149" s="3"/>
-      <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
-      <c r="I149" s="4"/>
-      <c r="J149" s="4"/>
-      <c r="K149" s="5"/>
-      <c r="L149" s="3"/>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A150" s="3"/>
-      <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
-      <c r="D150" s="5"/>
-      <c r="E150" s="5"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
-      <c r="I150" s="4"/>
-      <c r="J150" s="4"/>
-      <c r="K150" s="5"/>
-      <c r="L150" s="3"/>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A151" s="3"/>
-      <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
-      <c r="D151" s="5"/>
+      <c r="F148" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I148" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J148" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="K148" s="5" t="s">
+        <v>965</v>
+      </c>
+      <c r="L148" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A149" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B149" s="16" t="s">
+        <v>967</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>968</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>969</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="K149" s="5" t="s">
+        <v>970</v>
+      </c>
+      <c r="L149" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A150" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>974</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="I150" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J150" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K150" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="L150" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A151" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>979</v>
+      </c>
       <c r="E151" s="5"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
-      <c r="I151" s="4"/>
-      <c r="J151" s="4"/>
-      <c r="K151" s="5"/>
-      <c r="L151" s="3"/>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A152" s="3"/>
-      <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
-      <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="5"/>
-      <c r="L152" s="3"/>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A153" s="3"/>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="5"/>
-      <c r="E153" s="5"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
-      <c r="I153" s="4"/>
-      <c r="J153" s="4"/>
-      <c r="K153" s="5"/>
-      <c r="L153" s="3"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A154" s="3"/>
-      <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
-      <c r="D154" s="5"/>
-      <c r="E154" s="5"/>
-      <c r="F154" s="5"/>
-      <c r="G154" s="4"/>
-      <c r="H154" s="4"/>
-      <c r="I154" s="4"/>
-      <c r="J154" s="4"/>
-      <c r="K154" s="5"/>
-      <c r="L154" s="3"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A155" s="3"/>
-      <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
-      <c r="D155" s="5"/>
+      <c r="F151" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I151" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="J151" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K151" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="L151" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A152" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>984</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>985</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G152" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I152" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J152" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="K152" s="5" t="s">
+        <v>987</v>
+      </c>
+      <c r="L152" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A153" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>990</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>991</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I153" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J153" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K153" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="L153" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A154" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="I154" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="J154" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="K154" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L154" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A155" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>1005</v>
+      </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="4"/>
@@ -6754,7 +9221,7 @@
       <c r="K155" s="5"/>
       <c r="L155" s="3"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="3"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -6768,7 +9235,7 @@
       <c r="K156" s="5"/>
       <c r="L156" s="3"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="3"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -6782,7 +9249,7 @@
       <c r="K157" s="5"/>
       <c r="L157" s="3"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="3"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -6796,7 +9263,7 @@
       <c r="K158" s="5"/>
       <c r="L158" s="3"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" s="3"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -6810,7 +9277,7 @@
       <c r="K159" s="5"/>
       <c r="L159" s="3"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="3"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -6824,7 +9291,7 @@
       <c r="K160" s="5"/>
       <c r="L160" s="3"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" s="3"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -6838,7 +9305,7 @@
       <c r="K161" s="5"/>
       <c r="L161" s="3"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" s="3"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -6852,7 +9319,7 @@
       <c r="K162" s="5"/>
       <c r="L162" s="3"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" s="3"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -6866,7 +9333,7 @@
       <c r="K163" s="5"/>
       <c r="L163" s="3"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A164" s="3"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -6880,7 +9347,7 @@
       <c r="K164" s="5"/>
       <c r="L164" s="3"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" s="3"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -6894,7 +9361,7 @@
       <c r="K165" s="5"/>
       <c r="L165" s="3"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A166" s="3"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -6908,7 +9375,7 @@
       <c r="K166" s="5"/>
       <c r="L166" s="3"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" s="3"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -6922,7 +9389,7 @@
       <c r="K167" s="5"/>
       <c r="L167" s="3"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" s="3"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -6936,7 +9403,7 @@
       <c r="K168" s="5"/>
       <c r="L168" s="3"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" s="3"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -6950,7 +9417,7 @@
       <c r="K169" s="5"/>
       <c r="L169" s="3"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A170" s="3"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -6964,7 +9431,7 @@
       <c r="K170" s="5"/>
       <c r="L170" s="3"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" s="3"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -6978,7 +9445,7 @@
       <c r="K171" s="5"/>
       <c r="L171" s="3"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A172" s="3"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -6992,7 +9459,7 @@
       <c r="K172" s="5"/>
       <c r="L172" s="3"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" s="3"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -7006,7 +9473,7 @@
       <c r="K173" s="5"/>
       <c r="L173" s="3"/>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" s="3"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -7020,7 +9487,7 @@
       <c r="K174" s="5"/>
       <c r="L174" s="3"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" s="3"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -7034,7 +9501,7 @@
       <c r="K175" s="5"/>
       <c r="L175" s="3"/>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A176" s="3"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -7048,7 +9515,7 @@
       <c r="K176" s="5"/>
       <c r="L176" s="3"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" s="3"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -7062,7 +9529,7 @@
       <c r="K177" s="5"/>
       <c r="L177" s="3"/>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A178" s="3"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -7076,7 +9543,7 @@
       <c r="K178" s="5"/>
       <c r="L178" s="3"/>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" s="3"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -7090,7 +9557,7 @@
       <c r="K179" s="5"/>
       <c r="L179" s="3"/>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" s="3"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -7104,7 +9571,7 @@
       <c r="K180" s="5"/>
       <c r="L180" s="3"/>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" s="3"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -7118,7 +9585,7 @@
       <c r="K181" s="5"/>
       <c r="L181" s="3"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A182" s="3"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -7132,7 +9599,7 @@
       <c r="K182" s="5"/>
       <c r="L182" s="3"/>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A183" s="3"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -7146,7 +9613,7 @@
       <c r="K183" s="5"/>
       <c r="L183" s="3"/>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A184" s="3"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -7160,7 +9627,7 @@
       <c r="K184" s="5"/>
       <c r="L184" s="3"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A185" s="3"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -7174,7 +9641,7 @@
       <c r="K185" s="5"/>
       <c r="L185" s="3"/>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A186" s="3"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -7188,7 +9655,7 @@
       <c r="K186" s="5"/>
       <c r="L186" s="3"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A187" s="3"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -7202,7 +9669,7 @@
       <c r="K187" s="5"/>
       <c r="L187" s="3"/>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A188" s="3"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -7216,7 +9683,7 @@
       <c r="K188" s="5"/>
       <c r="L188" s="3"/>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A189" s="3"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -7230,7 +9697,7 @@
       <c r="K189" s="5"/>
       <c r="L189" s="3"/>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A190" s="3"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -7244,7 +9711,7 @@
       <c r="K190" s="5"/>
       <c r="L190" s="3"/>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A191" s="3"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -7258,7 +9725,7 @@
       <c r="K191" s="5"/>
       <c r="L191" s="3"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A192" s="3"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -7272,7 +9739,7 @@
       <c r="K192" s="5"/>
       <c r="L192" s="3"/>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A193" s="3"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -7286,7 +9753,7 @@
       <c r="K193" s="5"/>
       <c r="L193" s="3"/>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A194" s="3"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -7300,7 +9767,7 @@
       <c r="K194" s="5"/>
       <c r="L194" s="3"/>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A195" s="3"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -7314,7 +9781,7 @@
       <c r="K195" s="5"/>
       <c r="L195" s="3"/>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A196" s="3"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -7328,7 +9795,7 @@
       <c r="K196" s="5"/>
       <c r="L196" s="3"/>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A197" s="3"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -7342,7 +9809,7 @@
       <c r="K197" s="5"/>
       <c r="L197" s="3"/>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A198" s="3"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -7356,7 +9823,7 @@
       <c r="K198" s="5"/>
       <c r="L198" s="3"/>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A199" s="3"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -7370,7 +9837,7 @@
       <c r="K199" s="5"/>
       <c r="L199" s="3"/>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A200" s="3"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -7384,7 +9851,7 @@
       <c r="K200" s="5"/>
       <c r="L200" s="3"/>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A201" s="3"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -7398,7 +9865,7 @@
       <c r="K201" s="5"/>
       <c r="L201" s="3"/>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A202" s="3"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -7412,7 +9879,7 @@
       <c r="K202" s="5"/>
       <c r="L202" s="3"/>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A203" s="3"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -7426,7 +9893,7 @@
       <c r="K203" s="5"/>
       <c r="L203" s="3"/>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A204" s="3"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -7440,7 +9907,7 @@
       <c r="K204" s="5"/>
       <c r="L204" s="3"/>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A205" s="3"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -7454,7 +9921,7 @@
       <c r="K205" s="5"/>
       <c r="L205" s="3"/>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A206" s="3"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -7468,7 +9935,7 @@
       <c r="K206" s="5"/>
       <c r="L206" s="3"/>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -7482,7 +9949,7 @@
       <c r="K207" s="5"/>
       <c r="L207" s="3"/>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A208" s="3"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -7496,7 +9963,7 @@
       <c r="K208" s="5"/>
       <c r="L208" s="3"/>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A209" s="3"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -7510,7 +9977,7 @@
       <c r="K209" s="5"/>
       <c r="L209" s="3"/>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A210" s="3"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -7524,7 +9991,7 @@
       <c r="K210" s="5"/>
       <c r="L210" s="3"/>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A211" s="3"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -7538,7 +10005,7 @@
       <c r="K211" s="5"/>
       <c r="L211" s="3"/>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A212" s="3"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -7552,7 +10019,7 @@
       <c r="K212" s="5"/>
       <c r="L212" s="3"/>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A213" s="3"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -7566,7 +10033,7 @@
       <c r="K213" s="5"/>
       <c r="L213" s="3"/>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A214" s="3"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7580,7 +10047,7 @@
       <c r="K214" s="5"/>
       <c r="L214" s="3"/>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A215" s="3"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -7594,7 +10061,7 @@
       <c r="K215" s="5"/>
       <c r="L215" s="3"/>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A216" s="3"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -7608,7 +10075,7 @@
       <c r="K216" s="5"/>
       <c r="L216" s="3"/>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A217" s="3"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -7622,7 +10089,7 @@
       <c r="K217" s="5"/>
       <c r="L217" s="3"/>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A218" s="3"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -7636,7 +10103,7 @@
       <c r="K218" s="5"/>
       <c r="L218" s="3"/>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A219" s="3"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -7650,7 +10117,7 @@
       <c r="K219" s="5"/>
       <c r="L219" s="3"/>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A220" s="3"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -7664,7 +10131,7 @@
       <c r="K220" s="5"/>
       <c r="L220" s="3"/>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A221" s="3"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -7678,7 +10145,7 @@
       <c r="K221" s="5"/>
       <c r="L221" s="3"/>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A222" s="3"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -7692,7 +10159,7 @@
       <c r="K222" s="5"/>
       <c r="L222" s="3"/>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A223" s="3"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -7706,7 +10173,7 @@
       <c r="K223" s="5"/>
       <c r="L223" s="3"/>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A224" s="3"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -7720,7 +10187,7 @@
       <c r="K224" s="5"/>
       <c r="L224" s="3"/>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A225" s="3"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -7734,7 +10201,7 @@
       <c r="K225" s="5"/>
       <c r="L225" s="3"/>
     </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A226" s="3"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -7748,7 +10215,7 @@
       <c r="K226" s="5"/>
       <c r="L226" s="3"/>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="3"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -7762,7 +10229,7 @@
       <c r="K227" s="5"/>
       <c r="L227" s="3"/>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="3"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -7776,7 +10243,7 @@
       <c r="K228" s="5"/>
       <c r="L228" s="3"/>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A229" s="3"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -7790,7 +10257,7 @@
       <c r="K229" s="5"/>
       <c r="L229" s="3"/>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A230" s="3"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -7804,7 +10271,7 @@
       <c r="K230" s="5"/>
       <c r="L230" s="3"/>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="3"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -7818,7 +10285,7 @@
       <c r="K231" s="5"/>
       <c r="L231" s="3"/>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="3"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -7832,7 +10299,7 @@
       <c r="K232" s="5"/>
       <c r="L232" s="3"/>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="3"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -7846,7 +10313,7 @@
       <c r="K233" s="5"/>
       <c r="L233" s="3"/>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A234" s="3"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -7860,7 +10327,7 @@
       <c r="K234" s="5"/>
       <c r="L234" s="3"/>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A235" s="3"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -7874,7 +10341,7 @@
       <c r="K235" s="5"/>
       <c r="L235" s="3"/>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A236" s="3"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -7888,7 +10355,7 @@
       <c r="K236" s="5"/>
       <c r="L236" s="3"/>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A237" s="3"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -7902,7 +10369,7 @@
       <c r="K237" s="5"/>
       <c r="L237" s="3"/>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A238" s="3"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -7916,7 +10383,7 @@
       <c r="K238" s="5"/>
       <c r="L238" s="3"/>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A239" s="3"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -7930,7 +10397,7 @@
       <c r="K239" s="5"/>
       <c r="L239" s="3"/>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A240" s="3"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -7944,7 +10411,7 @@
       <c r="K240" s="5"/>
       <c r="L240" s="3"/>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A241" s="3"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -7958,7 +10425,7 @@
       <c r="K241" s="5"/>
       <c r="L241" s="3"/>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A242" s="3"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -7972,7 +10439,7 @@
       <c r="K242" s="5"/>
       <c r="L242" s="3"/>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A243" s="3"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -7986,7 +10453,7 @@
       <c r="K243" s="5"/>
       <c r="L243" s="3"/>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A244" s="3"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -8000,7 +10467,7 @@
       <c r="K244" s="5"/>
       <c r="L244" s="3"/>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A245" s="3"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -8014,7 +10481,7 @@
       <c r="K245" s="5"/>
       <c r="L245" s="3"/>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A246" s="3"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -8028,7 +10495,7 @@
       <c r="K246" s="5"/>
       <c r="L246" s="3"/>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A247" s="3"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -8042,7 +10509,7 @@
       <c r="K247" s="5"/>
       <c r="L247" s="3"/>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A248" s="3"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -8056,7 +10523,7 @@
       <c r="K248" s="5"/>
       <c r="L248" s="3"/>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A249" s="3"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -8070,7 +10537,7 @@
       <c r="K249" s="5"/>
       <c r="L249" s="3"/>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A250" s="3"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -8084,7 +10551,7 @@
       <c r="K250" s="5"/>
       <c r="L250" s="3"/>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A251" s="3"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -8098,7 +10565,7 @@
       <c r="K251" s="5"/>
       <c r="L251" s="3"/>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A252" s="3"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -8112,7 +10579,7 @@
       <c r="K252" s="5"/>
       <c r="L252" s="3"/>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A253" s="3"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -8126,7 +10593,7 @@
       <c r="K253" s="5"/>
       <c r="L253" s="3"/>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A254" s="3"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -8140,7 +10607,7 @@
       <c r="K254" s="5"/>
       <c r="L254" s="3"/>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A255" s="3"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -8154,7 +10621,7 @@
       <c r="K255" s="5"/>
       <c r="L255" s="3"/>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A256" s="3"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -8168,7 +10635,7 @@
       <c r="K256" s="5"/>
       <c r="L256" s="3"/>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A257" s="3"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -8182,7 +10649,7 @@
       <c r="K257" s="5"/>
       <c r="L257" s="3"/>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A258" s="3"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -8196,7 +10663,7 @@
       <c r="K258" s="5"/>
       <c r="L258" s="3"/>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A259" s="3"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -8210,7 +10677,7 @@
       <c r="K259" s="5"/>
       <c r="L259" s="3"/>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A260" s="3"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -8224,7 +10691,7 @@
       <c r="K260" s="5"/>
       <c r="L260" s="3"/>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A261" s="3"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -8238,7 +10705,7 @@
       <c r="K261" s="5"/>
       <c r="L261" s="3"/>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A262" s="3"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -8252,7 +10719,7 @@
       <c r="K262" s="5"/>
       <c r="L262" s="3"/>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A263" s="3"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -8266,7 +10733,7 @@
       <c r="K263" s="5"/>
       <c r="L263" s="3"/>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A264" s="3"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -8280,7 +10747,7 @@
       <c r="K264" s="5"/>
       <c r="L264" s="3"/>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A265" s="3"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -8294,7 +10761,7 @@
       <c r="K265" s="5"/>
       <c r="L265" s="3"/>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A266" s="3"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -8308,7 +10775,7 @@
       <c r="K266" s="5"/>
       <c r="L266" s="3"/>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A267" s="3"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -8322,7 +10789,7 @@
       <c r="K267" s="5"/>
       <c r="L267" s="3"/>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A268" s="3"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -8336,7 +10803,7 @@
       <c r="K268" s="5"/>
       <c r="L268" s="3"/>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A269" s="3"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -8350,7 +10817,7 @@
       <c r="K269" s="5"/>
       <c r="L269" s="3"/>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A270" s="3"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -8364,7 +10831,7 @@
       <c r="K270" s="5"/>
       <c r="L270" s="3"/>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A271" s="3"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -8378,7 +10845,7 @@
       <c r="K271" s="5"/>
       <c r="L271" s="3"/>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A272" s="3"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -8392,7 +10859,7 @@
       <c r="K272" s="5"/>
       <c r="L272" s="3"/>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A273" s="3"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -8406,7 +10873,7 @@
       <c r="K273" s="5"/>
       <c r="L273" s="3"/>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A274" s="3"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -8420,7 +10887,7 @@
       <c r="K274" s="5"/>
       <c r="L274" s="3"/>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A275" s="3"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -8434,7 +10901,7 @@
       <c r="K275" s="5"/>
       <c r="L275" s="3"/>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A276" s="3"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -8448,7 +10915,7 @@
       <c r="K276" s="5"/>
       <c r="L276" s="3"/>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A277" s="3"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -8462,7 +10929,7 @@
       <c r="K277" s="5"/>
       <c r="L277" s="3"/>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A278" s="3"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -8476,7 +10943,7 @@
       <c r="K278" s="5"/>
       <c r="L278" s="3"/>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A279" s="3"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -8490,7 +10957,7 @@
       <c r="K279" s="5"/>
       <c r="L279" s="3"/>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A280" s="3"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -8504,7 +10971,7 @@
       <c r="K280" s="5"/>
       <c r="L280" s="3"/>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A281" s="3"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -8518,7 +10985,7 @@
       <c r="K281" s="5"/>
       <c r="L281" s="3"/>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A282" s="3"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -8532,7 +10999,7 @@
       <c r="K282" s="5"/>
       <c r="L282" s="3"/>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A283" s="3"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -8546,7 +11013,7 @@
       <c r="K283" s="5"/>
       <c r="L283" s="3"/>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A284" s="3"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -8560,7 +11027,7 @@
       <c r="K284" s="5"/>
       <c r="L284" s="3"/>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A285" s="3"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -8574,7 +11041,7 @@
       <c r="K285" s="5"/>
       <c r="L285" s="3"/>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A286" s="3"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -8588,7 +11055,7 @@
       <c r="K286" s="5"/>
       <c r="L286" s="3"/>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A287" s="3"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -8602,7 +11069,7 @@
       <c r="K287" s="5"/>
       <c r="L287" s="3"/>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A288" s="3"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -8616,7 +11083,7 @@
       <c r="K288" s="5"/>
       <c r="L288" s="3"/>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A289" s="3"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -8630,7 +11097,7 @@
       <c r="K289" s="5"/>
       <c r="L289" s="3"/>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A290" s="3"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -8644,7 +11111,7 @@
       <c r="K290" s="5"/>
       <c r="L290" s="3"/>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A291" s="3"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -8658,7 +11125,7 @@
       <c r="K291" s="5"/>
       <c r="L291" s="3"/>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A292" s="3"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -8672,7 +11139,7 @@
       <c r="K292" s="5"/>
       <c r="L292" s="3"/>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A293" s="3"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -8686,7 +11153,7 @@
       <c r="K293" s="5"/>
       <c r="L293" s="3"/>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="3"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -8700,7 +11167,7 @@
       <c r="K294" s="5"/>
       <c r="L294" s="3"/>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A295" s="3"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -8714,7 +11181,7 @@
       <c r="K295" s="5"/>
       <c r="L295" s="3"/>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A296" s="3"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -8728,7 +11195,7 @@
       <c r="K296" s="5"/>
       <c r="L296" s="3"/>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A297" s="3"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -8742,7 +11209,7 @@
       <c r="K297" s="5"/>
       <c r="L297" s="3"/>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A298" s="3"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -8756,7 +11223,7 @@
       <c r="K298" s="5"/>
       <c r="L298" s="3"/>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A299" s="3"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -8770,7 +11237,7 @@
       <c r="K299" s="5"/>
       <c r="L299" s="3"/>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A300" s="3"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -8784,7 +11251,7 @@
       <c r="K300" s="5"/>
       <c r="L300" s="3"/>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A301" s="3"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -8798,7 +11265,7 @@
       <c r="K301" s="5"/>
       <c r="L301" s="3"/>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A302" s="3"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -8812,7 +11279,7 @@
       <c r="K302" s="5"/>
       <c r="L302" s="3"/>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A303" s="3"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -8826,7 +11293,7 @@
       <c r="K303" s="5"/>
       <c r="L303" s="3"/>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A304" s="3"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -8840,7 +11307,7 @@
       <c r="K304" s="5"/>
       <c r="L304" s="3"/>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="3"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -8854,7 +11321,7 @@
       <c r="K305" s="5"/>
       <c r="L305" s="3"/>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A306" s="3"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -8868,7 +11335,7 @@
       <c r="K306" s="5"/>
       <c r="L306" s="3"/>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A307" s="3"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -8882,7 +11349,7 @@
       <c r="K307" s="5"/>
       <c r="L307" s="3"/>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A308" s="3"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -8896,7 +11363,7 @@
       <c r="K308" s="5"/>
       <c r="L308" s="3"/>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A309" s="3"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -8910,7 +11377,7 @@
       <c r="K309" s="5"/>
       <c r="L309" s="3"/>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A310" s="3"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -8924,7 +11391,7 @@
       <c r="K310" s="5"/>
       <c r="L310" s="3"/>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A311" s="3"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -8938,7 +11405,7 @@
       <c r="K311" s="5"/>
       <c r="L311" s="3"/>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A312" s="3"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -8952,7 +11419,7 @@
       <c r="K312" s="5"/>
       <c r="L312" s="3"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A313" s="3"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -8966,7 +11433,7 @@
       <c r="K313" s="5"/>
       <c r="L313" s="3"/>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A314" s="3"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -8980,7 +11447,7 @@
       <c r="K314" s="5"/>
       <c r="L314" s="3"/>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A315" s="3"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -8994,7 +11461,7 @@
       <c r="K315" s="5"/>
       <c r="L315" s="3"/>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A316" s="3"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -9008,7 +11475,7 @@
       <c r="K316" s="5"/>
       <c r="L316" s="3"/>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A317" s="3"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -9022,7 +11489,7 @@
       <c r="K317" s="5"/>
       <c r="L317" s="3"/>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A318" s="3"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -9036,7 +11503,7 @@
       <c r="K318" s="5"/>
       <c r="L318" s="3"/>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A319" s="3"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -9050,7 +11517,7 @@
       <c r="K319" s="5"/>
       <c r="L319" s="3"/>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A320" s="3"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -9064,7 +11531,7 @@
       <c r="K320" s="5"/>
       <c r="L320" s="3"/>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A321" s="3"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -9078,7 +11545,7 @@
       <c r="K321" s="5"/>
       <c r="L321" s="3"/>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A322" s="3"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -9092,7 +11559,7 @@
       <c r="K322" s="5"/>
       <c r="L322" s="3"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A323" s="3"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -9106,7 +11573,7 @@
       <c r="K323" s="5"/>
       <c r="L323" s="3"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A324" s="3"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -9120,7 +11587,7 @@
       <c r="K324" s="5"/>
       <c r="L324" s="3"/>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A325" s="3"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -9134,7 +11601,7 @@
       <c r="K325" s="5"/>
       <c r="L325" s="3"/>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A326" s="3"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -9148,7 +11615,7 @@
       <c r="K326" s="5"/>
       <c r="L326" s="3"/>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A327" s="3"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -9162,7 +11629,7 @@
       <c r="K327" s="5"/>
       <c r="L327" s="3"/>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A328" s="3"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -9176,7 +11643,7 @@
       <c r="K328" s="5"/>
       <c r="L328" s="3"/>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A329" s="3"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -9190,7 +11657,7 @@
       <c r="K329" s="5"/>
       <c r="L329" s="3"/>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A330" s="3"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -9204,7 +11671,7 @@
       <c r="K330" s="5"/>
       <c r="L330" s="3"/>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A331" s="3"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -9218,7 +11685,7 @@
       <c r="K331" s="5"/>
       <c r="L331" s="3"/>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A332" s="3"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -9232,7 +11699,7 @@
       <c r="K332" s="5"/>
       <c r="L332" s="3"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A333" s="3"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -9246,7 +11713,7 @@
       <c r="K333" s="5"/>
       <c r="L333" s="3"/>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A334" s="3"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -9260,7 +11727,7 @@
       <c r="K334" s="5"/>
       <c r="L334" s="3"/>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A335" s="3"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -9274,7 +11741,7 @@
       <c r="K335" s="5"/>
       <c r="L335" s="3"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A336" s="3"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -9288,7 +11755,7 @@
       <c r="K336" s="5"/>
       <c r="L336" s="3"/>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A337" s="3"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -9302,7 +11769,7 @@
       <c r="K337" s="5"/>
       <c r="L337" s="3"/>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A338" s="3"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -9316,7 +11783,7 @@
       <c r="K338" s="5"/>
       <c r="L338" s="3"/>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A339" s="3"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -9330,7 +11797,7 @@
       <c r="K339" s="5"/>
       <c r="L339" s="3"/>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A340" s="3"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -9344,7 +11811,7 @@
       <c r="K340" s="5"/>
       <c r="L340" s="3"/>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A341" s="3"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -9358,7 +11825,7 @@
       <c r="K341" s="5"/>
       <c r="L341" s="3"/>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A342" s="3"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -9372,7 +11839,7 @@
       <c r="K342" s="5"/>
       <c r="L342" s="3"/>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A343" s="3"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -9386,7 +11853,7 @@
       <c r="K343" s="5"/>
       <c r="L343" s="3"/>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A344" s="3"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -9400,7 +11867,7 @@
       <c r="K344" s="5"/>
       <c r="L344" s="3"/>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A345" s="3"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -9414,7 +11881,7 @@
       <c r="K345" s="5"/>
       <c r="L345" s="3"/>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A346" s="3"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -9428,7 +11895,7 @@
       <c r="K346" s="5"/>
       <c r="L346" s="3"/>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A347" s="3"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -9442,7 +11909,7 @@
       <c r="K347" s="5"/>
       <c r="L347" s="3"/>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A348" s="3"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -9456,7 +11923,7 @@
       <c r="K348" s="5"/>
       <c r="L348" s="3"/>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A349" s="3"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -9470,7 +11937,7 @@
       <c r="K349" s="5"/>
       <c r="L349" s="3"/>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A350" s="3"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -9484,7 +11951,7 @@
       <c r="K350" s="5"/>
       <c r="L350" s="3"/>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A351" s="3"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -9498,7 +11965,7 @@
       <c r="K351" s="5"/>
       <c r="L351" s="3"/>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A352" s="3"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -9512,7 +11979,7 @@
       <c r="K352" s="5"/>
       <c r="L352" s="3"/>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A353" s="3"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -9526,7 +11993,7 @@
       <c r="K353" s="5"/>
       <c r="L353" s="3"/>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A354" s="3"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -9540,7 +12007,7 @@
       <c r="K354" s="5"/>
       <c r="L354" s="3"/>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A355" s="3"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -9554,7 +12021,7 @@
       <c r="K355" s="5"/>
       <c r="L355" s="3"/>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A356" s="3"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -9568,7 +12035,7 @@
       <c r="K356" s="5"/>
       <c r="L356" s="3"/>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A357" s="3"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -9582,7 +12049,7 @@
       <c r="K357" s="5"/>
       <c r="L357" s="3"/>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A358" s="3"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -9596,7 +12063,7 @@
       <c r="K358" s="5"/>
       <c r="L358" s="3"/>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A359" s="3"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -9610,7 +12077,7 @@
       <c r="K359" s="5"/>
       <c r="L359" s="3"/>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A360" s="3"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -9624,7 +12091,7 @@
       <c r="K360" s="5"/>
       <c r="L360" s="3"/>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A361" s="3"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -9638,7 +12105,7 @@
       <c r="K361" s="5"/>
       <c r="L361" s="3"/>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A362" s="3"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -9652,7 +12119,7 @@
       <c r="K362" s="5"/>
       <c r="L362" s="3"/>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A363" s="3"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -9666,7 +12133,7 @@
       <c r="K363" s="5"/>
       <c r="L363" s="3"/>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A364" s="3"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -9680,7 +12147,7 @@
       <c r="K364" s="5"/>
       <c r="L364" s="3"/>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A365" s="3"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -9694,7 +12161,7 @@
       <c r="K365" s="5"/>
       <c r="L365" s="3"/>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A366" s="3"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -9708,7 +12175,7 @@
       <c r="K366" s="5"/>
       <c r="L366" s="3"/>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A367" s="3"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -9722,7 +12189,7 @@
       <c r="K367" s="5"/>
       <c r="L367" s="3"/>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A368" s="3"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -9736,7 +12203,7 @@
       <c r="K368" s="5"/>
       <c r="L368" s="3"/>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A369" s="3"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -9750,7 +12217,7 @@
       <c r="K369" s="5"/>
       <c r="L369" s="3"/>
     </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A370" s="3"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -9764,6 +12231,20 @@
       <c r="K370" s="5"/>
       <c r="L370" s="3"/>
     </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A371" s="3"/>
+      <c r="B371" s="4"/>
+      <c r="C371" s="4"/>
+      <c r="D371" s="5"/>
+      <c r="E371" s="5"/>
+      <c r="F371" s="5"/>
+      <c r="G371" s="4"/>
+      <c r="H371" s="4"/>
+      <c r="I371" s="4"/>
+      <c r="J371" s="4"/>
+      <c r="K371" s="5"/>
+      <c r="L371" s="3"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L2" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB30DD9-90BA-4863-988D-946263078CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB8A1D5-32AB-4F4A-B8EA-46ADCAF2A263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/1. skill_area [13-17,5]/15. version_wip.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\1. skill_area [13-17,5]\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dproc\Desktop\Disertatie Gabi\2. Workspace\dml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EB8A1D5-32AB-4F4A-B8EA-46ADCAF2A263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D63F5E-6A43-439E-B729-9772BF80D0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="version" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="1006">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2440" uniqueCount="1409">
   <si>
     <t>name</t>
   </si>
@@ -3049,6 +3049,1218 @@
   </si>
   <si>
     <t>Stable API, improved routing, view engines, authentication modules, better hosting</t>
+  </si>
+  <si>
+    <t>No async/await support, limited enterprise adoption</t>
+  </si>
+  <si>
+    <t>First stable release widely adopted for lightweight microservices and prototypes.</t>
+  </si>
+  <si>
+    <t>NancyFX 1.4</t>
+  </si>
+  <si>
+    <t>2015-12-18</t>
+  </si>
+  <si>
+    <t>2019-12-31</t>
+  </si>
+  <si>
+    <t>Better hosting, improved DI, enhanced testing support, bug fixes</t>
+  </si>
+  <si>
+    <t>No .NET Core support, stagnating ecosystem</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>Most stable and widely used version before the .NET Core transition era.</t>
+  </si>
+  <si>
+    <t>NancyFX 2.0</t>
+  </si>
+  <si>
+    <t>2017-11-15</t>
+  </si>
+  <si>
+    <t>2020-12-31</t>
+  </si>
+  <si>
+    <t>Partial .NET Core support, improved pipelines, better modularity</t>
+  </si>
+  <si>
+    <t>roject discontinued, incomplete .NET Core integration</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Final release attempting .NET Core support before the project was officially archived.</t>
+  </si>
+  <si>
+    <t>Django 2.2</t>
+  </si>
+  <si>
+    <t>2019-04-01</t>
+  </si>
+  <si>
+    <t>2022-04-11</t>
+  </si>
+  <si>
+    <t>Python 3-only, improved ORM, better URL routing, performance improvements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No async support, older template engine limitations
+</t>
+  </si>
+  <si>
+    <t>Django Software Foundation</t>
+  </si>
+  <si>
+    <t>Stable LTS release widely used in enterprise and large-scale web applications.</t>
+  </si>
+  <si>
+    <t>Django 3.0</t>
+  </si>
+  <si>
+    <t>2019-12-02</t>
+  </si>
+  <si>
+    <t>2021-04-06</t>
+  </si>
+  <si>
+    <t>ASGI support, improved JSONField, modernized internals</t>
+  </si>
+  <si>
+    <t>Partial async support, ecosystem catching up</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>First step toward full async capabilities with ASGI integration.</t>
+  </si>
+  <si>
+    <t>Django 3.2</t>
+  </si>
+  <si>
+    <t>2024-04-01</t>
+  </si>
+  <si>
+    <t>Auto-generated AppConfig, improved ORM, async views, performance boosts</t>
+  </si>
+  <si>
+    <t>Limited async ORM, no full async stack</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>Popular LTS release with strong stability and modern Python support.</t>
+  </si>
+  <si>
+    <t>Django 4.0</t>
+  </si>
+  <si>
+    <t>2021-12-07</t>
+  </si>
+  <si>
+    <t>2023-04-01</t>
+  </si>
+  <si>
+    <t>Python 3.10 support, improved forms, new Redis cache backend</t>
+  </si>
+  <si>
+    <t>Async ORM still missing</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>Modernized release with better performance and updated Python compatibility.</t>
+  </si>
+  <si>
+    <t>Django 4.2</t>
+  </si>
+  <si>
+    <t>2023-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>Async ORM queries (partial), form rendering improvements, template engine updates</t>
+  </si>
+  <si>
+    <t>Full async ORM still in progress</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Strong LTS release with major async improvements and long-term stability.</t>
+  </si>
+  <si>
+    <t>Django 5.0</t>
+  </si>
+  <si>
+    <t>2023-12-04</t>
+  </si>
+  <si>
+    <t>2025-04-01</t>
+  </si>
+  <si>
+    <t>Better async support, improved ORM, modernized middleware</t>
+  </si>
+  <si>
+    <t>Still not fully async end-to-end</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>Major modernization release pushing Django closer to a fully async architecture.</t>
+  </si>
+  <si>
+    <t>Django 5.1</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>Expanded async ORM, improved caching, better security defaults</t>
+  </si>
+  <si>
+    <t>Async migrations still limited</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>Incremental improvements with stronger async capabilities and performance enhancements.</t>
+  </si>
+  <si>
+    <t>Flask 0.12</t>
+  </si>
+  <si>
+    <t>2016-12-21</t>
+  </si>
+  <si>
+    <t>2018-12-31</t>
+  </si>
+  <si>
+    <t>Python 3 support improvements, better CLI, security fixes</t>
+  </si>
+  <si>
+    <t>Limited async support, outdated Werkzeug/Jinja versions</t>
+  </si>
+  <si>
+    <t>Armin Ronacher</t>
+  </si>
+  <si>
+    <t>Flask 1.1</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>Better JSON handling, improved routing, performance improvements</t>
+  </si>
+  <si>
+    <t>Mature pre‑1.0 release widely used for lightweight microservices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Still lacks async capabilities, ecosystem fragmentation</t>
+  </si>
+  <si>
+    <t>Highly stable release used extensively in enterprise microservices.</t>
+  </si>
+  <si>
+    <t>Pallets Team</t>
+  </si>
+  <si>
+    <t>Flask 2.2</t>
+  </si>
+  <si>
+    <t>2022-08-09</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>Full async views, improved CLI, enhanced debugging and error handling</t>
+  </si>
+  <si>
+    <t>No async ORM, async ecosystem still maturing</t>
+  </si>
+  <si>
+    <t>Mature async-enabled release with strong developer experience improvements.</t>
+  </si>
+  <si>
+    <t>Flask 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2024-09-15</t>
+  </si>
+  <si>
+    <t>Async improvements, better extension APIs, performance optimizations</t>
+  </si>
+  <si>
+    <t>Async ecosystem still evolving, limited built-in tooling for large-scale apps</t>
+  </si>
+  <si>
+    <t>Incremental upgrade with stronger async capabilities and improved performance.</t>
+  </si>
+  <si>
+    <t>FastAPI 0.115.0</t>
+  </si>
+  <si>
+    <t>2024-02-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2026-12-31</t>
+  </si>
+  <si>
+    <t>Improved WebSocket handling, better dependency injection performance, enhanced OpenAPI generation</t>
+  </si>
+  <si>
+    <t>Limited built-in ORM support, async database tooling still fragmented</t>
+  </si>
+  <si>
+    <t>Sebastián Ramírez</t>
+  </si>
+  <si>
+    <t>Mature pre‑1.0 release widely adopted for high‑performance async APIs and microservices.</t>
+  </si>
+  <si>
+    <t>FastAPI 1.0.0</t>
+  </si>
+  <si>
+    <t>2023-12-05</t>
+  </si>
+  <si>
+    <t>Stable API guarantees, improved validation, enhanced async support, better Pydantic v2 integration</t>
+  </si>
+  <si>
+    <t>Still lacks built-in background task orchestration, ecosystem depends heavily on third‑party libraries</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> First stable major release, widely adopted in production for scalable async services.</t>
+  </si>
+  <si>
+    <t>FastAPI 2.0.0</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2029-12-31</t>
+  </si>
+  <si>
+    <t>Full Pydantic v2 optimization, improved routing performance, enhanced dependency injection, better async streaming</t>
+  </si>
+  <si>
+    <t>Still no native ORM, async database ecosystem remains inconsistent</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Major modernization release focused on performance, async improvements, and Pydantic v2 integration.</t>
+  </si>
+  <si>
+    <t>Pyramid 1.10</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>Improved routing, better configuration system, enhanced security defaults</t>
+  </si>
+  <si>
+    <t>Limited async support, smaller ecosystem compared to Flask and Django</t>
+  </si>
+  <si>
+    <t>Pylons Project</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mature and stable release widely used for flexible, modular Python web applications.</t>
+  </si>
+  <si>
+    <t>Pyramid 2.0</t>
+  </si>
+  <si>
+    <t>2020-12-15</t>
+  </si>
+  <si>
+    <t>Python 3‑only, improved type hints, modernized configuration, updated security features</t>
+  </si>
+  <si>
+    <t>No native async support, declining community adoption</t>
+  </si>
+  <si>
+    <t>Modernized release focusing on Python 3 compatibility and improved developer experience.</t>
+  </si>
+  <si>
+    <t>Pyramid 3.0</t>
+  </si>
+  <si>
+    <t>2023-05-10</t>
+  </si>
+  <si>
+    <t>Updated dependency stack, improved configuration API, better extensibility</t>
+  </si>
+  <si>
+    <t>Still lacks async support, ecosystem continues to shrink</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>Latest stable release focused on maintainability and modernization of the framework.</t>
+  </si>
+  <si>
+    <t>Tornado 4.5.3</t>
+  </si>
+  <si>
+    <t>2017-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2020-12-31</t>
+  </si>
+  <si>
+    <t>Improved HTTP server performance, better SSL support, enhanced coroutine handling</t>
+  </si>
+  <si>
+    <t>Outdated coroutine syntax, limited ecosystem compared to modern async frameworks</t>
+  </si>
+  <si>
+    <t>Facebook / FriendFeed</t>
+  </si>
+  <si>
+    <t>Mature async web framework release widely used for real‑time applications and long‑lived connections.</t>
+  </si>
+  <si>
+    <t>Tornado 5.1</t>
+  </si>
+  <si>
+    <t>2018-07-03</t>
+  </si>
+  <si>
+    <t>Native asyncio integration, improved event loop support, better Windows compatibility</t>
+  </si>
+  <si>
+    <t>Migration complexity from older coroutine patterns, limited high‑level abstractions</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>Important transition release introducing full asyncio support and modern async patterns.</t>
+  </si>
+  <si>
+    <t>Tornado 6.4</t>
+  </si>
+  <si>
+    <t>2023-11-15</t>
+  </si>
+  <si>
+    <t>Python 3.8+ only, improved asyncio performance, updated HTTP/2 support, better security defaults</t>
+  </si>
+  <si>
+    <t>Smaller ecosystem, lacks modern tooling compared to FastAPI or Starlette</t>
+  </si>
+  <si>
+    <t>Modern stable release focused on performance, asyncio improvements, and long‑term maintainability.</t>
+  </si>
+  <si>
+    <t>Express.js 3.21.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2015-06-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2017-12-31</t>
+  </si>
+  <si>
+    <t>Improved routing stability, better middleware handling, enhanced error management</t>
+  </si>
+  <si>
+    <t>Outdated architecture, lacks modern middleware patterns, no async/await support</t>
+  </si>
+  <si>
+    <t>TJ Holowaychuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Final stable release of the 3.x series, widely used before the major 4.x architectural changes.</t>
+  </si>
+  <si>
+    <t>Express.js 4.19.2</t>
+  </si>
+  <si>
+    <t>2024-03-15</t>
+  </si>
+  <si>
+    <t>Updated routing engine, improved security defaults, better middleware flexibility</t>
+  </si>
+  <si>
+    <t>No built‑in async middleware, relies heavily on third‑party ecosystem</t>
+  </si>
+  <si>
+    <t>Express.js Team</t>
+  </si>
+  <si>
+    <t>Most widely used Express.js release, powering the majority of Node.js REST APIs in production.</t>
+  </si>
+  <si>
+    <t>Express.js 5.0.1</t>
+  </si>
+  <si>
+    <t>Async route handlers, improved error handling, modernized router, updated dependency stack</t>
+  </si>
+  <si>
+    <t>Still minimalistic, lacks built‑in validation and structured middleware patterns</t>
+  </si>
+  <si>
+    <t>First major update in years, bringing async/await support and modern Node.js compatibility.</t>
+  </si>
+  <si>
+    <t>NestJS 7.6.18</t>
+  </si>
+  <si>
+    <t>2021-02-15</t>
+  </si>
+  <si>
+    <t>Improved dependency injection, enhanced interceptors, better testing utilities</t>
+  </si>
+  <si>
+    <t>Limited support for advanced microservice patterns, older RxJS integration</t>
+  </si>
+  <si>
+    <t>Kamil Myśliwiec</t>
+  </si>
+  <si>
+    <t>Mature release widely used for scalable TypeScript backend applications.</t>
+  </si>
+  <si>
+    <t>NestJS 8.4.7</t>
+  </si>
+  <si>
+    <t>2022-06-20</t>
+  </si>
+  <si>
+    <t>Enhanced performance, improved middleware system, better GraphQL and WebSockets support</t>
+  </si>
+  <si>
+    <t>Complex learning curve for beginners, heavy reliance on decorators</t>
+  </si>
+  <si>
+    <t>Feature-rich release improving performance and developer experience across modules.</t>
+  </si>
+  <si>
+    <t>NestJS 9.4.3</t>
+  </si>
+  <si>
+    <t>2023-07-10</t>
+  </si>
+  <si>
+    <t>Better modularity, improved CLI, enhanced microservices layer, updated caching module</t>
+  </si>
+  <si>
+    <t>Still verbose for small projects, dependency injection complexity</t>
+  </si>
+  <si>
+    <t>Modern release focused on microservices, modularity, and improved tooling.</t>
+  </si>
+  <si>
+    <t>NestJS 10.3.2</t>
+  </si>
+  <si>
+    <t>2024-11-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Improved performance, enhanced module federation, better caching, updated GraphQL and WebSockets integration</t>
+  </si>
+  <si>
+    <t>Still requires significant boilerplate, steep learning curve for newcomers</t>
+  </si>
+  <si>
+    <t>Latest major release with strong focus on performance, modularity, and enterprise‑grade scalability.</t>
+  </si>
+  <si>
+    <t>Koa 1.6.2</t>
+  </si>
+  <si>
+    <t>2017-03-15</t>
+  </si>
+  <si>
+    <t>Generator‑based middleware, improved error handling, lightweight core</t>
+  </si>
+  <si>
+    <t>Generator functions outdated, no async/await support, limited ecosystem</t>
+  </si>
+  <si>
+    <t>Koa Team (original Express.js authors)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Final generator‑based release before the transition to async/await in Koa 2.x.</t>
+  </si>
+  <si>
+    <t>Koa 2.15.3</t>
+  </si>
+  <si>
+    <t>2023-11-10</t>
+  </si>
+  <si>
+    <t>Full async/await middleware, improved context handling, updated dependency stack</t>
+  </si>
+  <si>
+    <t>Minimalistic core requires many third‑party modules, smaller ecosystem than Express</t>
+  </si>
+  <si>
+    <t>Koa Team</t>
+  </si>
+  <si>
+    <t>Mature async‑first release widely used for lightweight and high‑performance Node.js APIs.</t>
+  </si>
+  <si>
+    <t>Koa 3.0.0</t>
+  </si>
+  <si>
+    <t>2024-09-20</t>
+  </si>
+  <si>
+    <t>Improved middleware composition, enhanced TypeScript support, better error propagation, updated HTTP handling</t>
+  </si>
+  <si>
+    <t>Still lacks built‑in routing and validation, ecosystem smaller than Express or Fastify</t>
+  </si>
+  <si>
+    <t>Modern release focused on TypeScript, performance, and improved developer experience.</t>
+  </si>
+  <si>
+    <t>Hapi.js 16.7.0</t>
+  </si>
+  <si>
+    <t>2017-07-20</t>
+  </si>
+  <si>
+    <t>Improved plugin system, better request lifecycle, enhanced validation</t>
+  </si>
+  <si>
+    <t>Callback‑based architecture, no async/await support, outdated patterns</t>
+  </si>
+  <si>
+    <t>Eran Hammer</t>
+  </si>
+  <si>
+    <t>Final callback‑based release before the major async rewrite in version 17.</t>
+  </si>
+  <si>
+    <t>Hapi.js 17.9.0</t>
+  </si>
+  <si>
+    <t>2018-10-15</t>
+  </si>
+  <si>
+    <t>Full async/await rewrite, simplified server API, improved plugin architecture</t>
+  </si>
+  <si>
+    <t>Smaller ecosystem than Express, steeper learning curve</t>
+  </si>
+  <si>
+    <t>Major rewrite introducing async/await and modernizing the entire framework.</t>
+  </si>
+  <si>
+    <t>Hapi.js 18.1.0</t>
+  </si>
+  <si>
+    <t>2019-03-12</t>
+  </si>
+  <si>
+    <t>Improved security defaults, better validation, updated plugin APIs</t>
+  </si>
+  <si>
+    <t>Still less popular than Express or Fastify, limited middleware ecosystem</t>
+  </si>
+  <si>
+    <t>Stability‑focused release improving security and developer experience.</t>
+  </si>
+  <si>
+    <t>Hapi.js 19.2.0</t>
+  </si>
+  <si>
+    <t>2020-04-15</t>
+  </si>
+  <si>
+    <t>Updated dependencies, improved routing performance, enhanced request lifecycle</t>
+  </si>
+  <si>
+    <t>Smaller community, fewer modern integrations</t>
+  </si>
+  <si>
+    <t>Performance‑oriented release with incremental improvements across the framework.</t>
+  </si>
+  <si>
+    <t>Hapi.js 20.3.0</t>
+  </si>
+  <si>
+    <t>2021-11-10</t>
+  </si>
+  <si>
+    <t>Better TypeScript support, improved plugin isolation, enhanced validation engine</t>
+  </si>
+  <si>
+    <t>Still less ergonomic than newer Node.js frameworks</t>
+  </si>
+  <si>
+    <t>Modern release focusing on TypeScript, security, and plugin architecture improvements.</t>
+  </si>
+  <si>
+    <t>Hapi.js 21.3.2</t>
+  </si>
+  <si>
+    <t>2024-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Updated HTTP handling, improved performance, enhanced TypeScript definitions, better plugin lifecycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smaller ecosystem, fewer integrations compared to Express or Fastify</t>
+  </si>
+  <si>
+    <t>Latest stable release with strong focus on performance, TypeScript, and maintainability.</t>
+  </si>
+  <si>
+    <t>AdonisJS 4.1.0</t>
+  </si>
+  <si>
+    <t>2019-02-12</t>
+  </si>
+  <si>
+    <t>Improved ORM (Lucid), better authentication system, enhanced routing and middleware</t>
+  </si>
+  <si>
+    <t>Limited TypeScript support, monolithic structure less flexible than modern frameworks</t>
+  </si>
+  <si>
+    <t>Harminder Virk</t>
+  </si>
+  <si>
+    <t>Stable release widely used for MVC‑style Node.js applications with strong conventions.</t>
+  </si>
+  <si>
+    <t>AdonisJS 5.9.0</t>
+  </si>
+  <si>
+    <t>2022-11-18</t>
+  </si>
+  <si>
+    <t>Full TypeScript rewrite, improved IoC container, better HTTP layer, enhanced validation</t>
+  </si>
+  <si>
+    <t>Steeper learning curve due to strong conventions, smaller ecosystem than Express/Nest</t>
+  </si>
+  <si>
+    <t>Major modernization release introducing TypeScript‑first architecture and improved developer experience.</t>
+  </si>
+  <si>
+    <t>AdonisJS 6.3.0</t>
+  </si>
+  <si>
+    <t>Enhanced modular architecture, improved ORM performance, better caching, updated routing engine</t>
+  </si>
+  <si>
+    <t>Still niche compared to larger Node.js ecosystems, requires adherence to strict conventions</t>
+  </si>
+  <si>
+    <t>Latest stable release focused on performance, modularity, and enterprise‑grade TypeScript development.</t>
+  </si>
+  <si>
+    <t>Gin 1.10.0</t>
+  </si>
+  <si>
+    <t>Improved routing performance, enhanced middleware engine, updated JSON rendering, better error handling</t>
+  </si>
+  <si>
+    <t>Limited built‑in tooling, relies heavily on third‑party libraries for advanced features</t>
+  </si>
+  <si>
+    <t>Gin‑Gonic Team</t>
+  </si>
+  <si>
+    <t>High‑performance HTTP web framework for Go, widely used for microservices and REST APIs due to its speed and simplicity.</t>
+  </si>
+  <si>
+    <t>Echo 3.3.10</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>Improved middleware chaining, enhanced routing performance, better error handling</t>
+  </si>
+  <si>
+    <t>Limited native support for advanced patterns, older API design compared to v4</t>
+  </si>
+  <si>
+    <t>Labstack Team</t>
+  </si>
+  <si>
+    <t>Stable and widely used release before the major architectural improvements in Echo v4.</t>
+  </si>
+  <si>
+    <t>Echo 4.12.0</t>
+  </si>
+  <si>
+    <t>2024-02-20</t>
+  </si>
+  <si>
+    <t>Improved routing engine, enhanced middleware API, better JSON encoding, updated HTTP/2 support</t>
+  </si>
+  <si>
+    <t>Still minimalistic, relies on external libraries for ORM, validation, and advanced tooling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Modern high‑performance release widely used for Go microservices and REST APIs, known for speed and simplicity.</t>
+  </si>
+  <si>
+    <t>Fiber 1.14.6</t>
+  </si>
+  <si>
+    <t>Improved routing performance, enhanced middleware system, better error handling</t>
+  </si>
+  <si>
+    <t>Limited ecosystem maturity, fewer integrations compared to Gin or Echo</t>
+  </si>
+  <si>
+    <t>Fiber Team (Fasthttp-based)</t>
+  </si>
+  <si>
+    <t>High‑performance early release built on Fasthttp, focused on speed and simplicity.</t>
+  </si>
+  <si>
+    <t>Fiber 2.52.0</t>
+  </si>
+  <si>
+    <t>2023-10-05</t>
+  </si>
+  <si>
+    <t>Improved routing engine, enhanced middleware API, better JSON encoding, updated template engine</t>
+  </si>
+  <si>
+    <t>Still relies heavily on third‑party libraries for advanced features, limited built‑in tooling</t>
+  </si>
+  <si>
+    <t>Fiber Team</t>
+  </si>
+  <si>
+    <t>Mature and widely adopted release known for exceptional performance and developer‑friendly API.</t>
+  </si>
+  <si>
+    <t>Fiber 3.0.0</t>
+  </si>
+  <si>
+    <t>2024-09-12</t>
+  </si>
+  <si>
+    <t>Improved modular architecture, enhanced middleware pipeline, better TypeScript‑style generics for Go 1.22+, updated HTTP/2 and WebSocket support</t>
+  </si>
+  <si>
+    <t>Still minimalistic, lacks built‑in ORM or validation, ecosystem smaller than Gin</t>
+  </si>
+  <si>
+    <t>Modern high‑performance release focused on modularity, speed, and improved developer experience.</t>
+  </si>
+  <si>
+    <t>Beego 1.12.3</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>Improved MVC structure, enhanced ORM (BeeORM), better logging, updated router</t>
+  </si>
+  <si>
+    <t>Heavy framework compared to modern Go microframeworks, slower compile times, limited modularity</t>
+  </si>
+  <si>
+    <t>Beego Team (Aston Zhang)</t>
+  </si>
+  <si>
+    <t>Mature MVC‑style Go framework widely used for enterprise applications with built‑in ORM, caching, and session management.</t>
+  </si>
+  <si>
+    <t>Beego 2.2.0</t>
+  </si>
+  <si>
+    <t>2024-03-22</t>
+  </si>
+  <si>
+    <t>Improved modular architecture, enhanced BeeORM performance, better dependency injection, updated router and middleware system</t>
+  </si>
+  <si>
+    <t>Still heavier than minimalist Go frameworks, smaller ecosystem compared to Gin or Fiber</t>
+  </si>
+  <si>
+    <t>Beego Team</t>
+  </si>
+  <si>
+    <t>Modernized release focused on modularity, performance, and enterprise‑grade tooling for Go applications.</t>
+  </si>
+  <si>
+    <t>Revel 0.21.0</t>
+  </si>
+  <si>
+    <t>2020-04-18</t>
+  </si>
+  <si>
+    <t>Improved hot‑reload engine, enhanced routing, better controller lifecycle, updated template engine</t>
+  </si>
+  <si>
+    <t>Heavy framework compared to modern Go microframeworks, slower compile times, limited ecosystem growth</t>
+  </si>
+  <si>
+    <t>Revel Team</t>
+  </si>
+  <si>
+    <t>Mature pre‑1.0 release offering a full MVC framework for Go, including routing, controllers, templates, and hot reload.</t>
+  </si>
+  <si>
+    <t>Revel 1.0.0</t>
+  </si>
+  <si>
+    <t>Modernized module system, improved template engine, enhanced routing performance, better testing tools</t>
+  </si>
+  <si>
+    <t>Still heavier and less flexible than Gin/Echo/Fiber, smaller community, slower adoption</t>
+  </si>
+  <si>
+    <t>First stable major release focusing on modernization, improved performance, and better developer experience for full‑stack Go MVC applications.</t>
+  </si>
+  <si>
+    <t>Ruby on Rails 4.2.11.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2019-03-13</t>
+  </si>
+  <si>
+    <t>ActiveJob improvements, better caching, enhanced security patches</t>
+  </si>
+  <si>
+    <t>Outdated architecture, lacks modern async features, older Ruby compatibility</t>
+  </si>
+  <si>
+    <t>David Heinemeier Hansson (DHH)</t>
+  </si>
+  <si>
+    <t>Final stable release of the 4.x series, widely used in legacy Rails applications.</t>
+  </si>
+  <si>
+    <t>Ruby on Rails 5.2.8.1</t>
+  </si>
+  <si>
+    <t>2022-07-12</t>
+  </si>
+  <si>
+    <t>ActiveStorage, improved credentials management, better caching and performance</t>
+  </si>
+  <si>
+    <t>Limited async support, monolithic structure less flexible than modern frameworks</t>
+  </si>
+  <si>
+    <t>Mature release introducing modern file storage and improved security features.</t>
+  </si>
+  <si>
+    <t>Ruby on Rails 6.1.7.7</t>
+  </si>
+  <si>
+    <t>2024-01-16</t>
+  </si>
+  <si>
+    <t>Improved ActionMailbox, ActionText, multi‑DB support, better parallel testing</t>
+  </si>
+  <si>
+    <t>Still limited native async capabilities, heavy monolithic architecture</t>
+  </si>
+  <si>
+    <t>Feature‑rich release widely used in enterprise applications with strong multi‑database support.</t>
+  </si>
+  <si>
+    <t>Ruby on Rails 7.1.3.2</t>
+  </si>
+  <si>
+    <t>2024-03-20</t>
+  </si>
+  <si>
+    <t>Improved Hotwire/Turbo, better encryption, enhanced ActiveRecord performance, async query support</t>
+  </si>
+  <si>
+    <t>till opinionated and monolithic, requires deep Rails conventions knowledge</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>Modern release focused on performance, Hotwire integration, and improved developer experience.</t>
+  </si>
+  <si>
+    <t>Sinatra 1.4.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2017-01-17</t>
+  </si>
+  <si>
+    <t>Improved routing stability, better middleware integration, enhanced template rendering</t>
+  </si>
+  <si>
+    <t>Limited scalability for large apps, lacks built‑in ORM or structure, minimal ecosystem</t>
+  </si>
+  <si>
+    <t>Blake Mizerany</t>
+  </si>
+  <si>
+    <t>Final stable release of the 1.x series, widely used for small Ruby services and micro‑APIs.</t>
+  </si>
+  <si>
+    <t>Sinatra 2.2.4</t>
+  </si>
+  <si>
+    <t>2024-02-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Improved Rack integration, better performance, updated Ruby compatibility, enhanced security patches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still minimalistic, lacks built‑in structure, not ideal for large enterprise applications
+</t>
+  </si>
+  <si>
+    <t>Modern stable release focused on performance, simplicity, and compatibility with the latest Ruby versions.</t>
+  </si>
+  <si>
+    <t>Laravel 5.8</t>
+  </si>
+  <si>
+    <t>2019-02-26</t>
+  </si>
+  <si>
+    <t>2020-02-26</t>
+  </si>
+  <si>
+    <t>Improved email validation, automatic policy discovery, enhanced caching</t>
+  </si>
+  <si>
+    <t>Outdated PHP version support, lacks modern type safety, older architecture</t>
+  </si>
+  <si>
+    <t>Taylor Otwell</t>
+  </si>
+  <si>
+    <t>Final release of the 5.x series, widely used in legacy enterprise applications.</t>
+  </si>
+  <si>
+    <t>Laravel 6.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2020-12-08</t>
+  </si>
+  <si>
+    <t>2022-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Semantic versioning, improved job middleware, enhanced authorization responses</t>
+  </si>
+  <si>
+    <t>Limited type hints, older PHP compatibility, lacks modern features from 8+</t>
+  </si>
+  <si>
+    <t>First LTS release under semantic versioning, widely adopted in stable enterprise environments.</t>
+  </si>
+  <si>
+    <t>Laravel 7.30</t>
+  </si>
+  <si>
+    <t>2021-03-03</t>
+  </si>
+  <si>
+    <t>Laravel Sanctum, improved routing speed, Blade component tags</t>
+  </si>
+  <si>
+    <t>Short support window, lacks modern PHP 8 features</t>
+  </si>
+  <si>
+    <t>Feature‑rich release introducing Sanctum and modern Blade components.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Laravel 8.83</t>
+  </si>
+  <si>
+    <t>2022-02-08</t>
+  </si>
+  <si>
+    <t>2023-01-24</t>
+  </si>
+  <si>
+    <t>Laravel Jetstream, improved factories, model directory restructuring</t>
+  </si>
+  <si>
+    <t>No native typed properties, older PHP compatibility</t>
+  </si>
+  <si>
+    <t>Major release introducing Jetstream and modern application scaffolding.</t>
+  </si>
+  <si>
+    <t>Laravel 9.52</t>
+  </si>
+  <si>
+    <t>2023-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2025-02-04</t>
+  </si>
+  <si>
+    <t>PHP 8.1 support, improved route caching, Flysystem v3, enhanced Eloquent performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Still monolithic for microservices, heavy for small apps
+</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>LTS release with strong performance improvements and modern PHP features.</t>
+  </si>
+  <si>
+    <t>Laravel 10.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2024-03-12</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>Native type declarations, improved process layer, enhanced validation, better test coverage</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Still opinionated, requires strong adherence to Laravel conventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modern release focused on type safety, performance, and developer </t>
+  </si>
+  <si>
+    <t>Laravel 11.9</t>
+  </si>
+  <si>
+    <t>2025-02-18</t>
+  </si>
+  <si>
+    <t>2030-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slimmer application skeleton, improved queue system, enhanced Eloquent performance, better modularity</t>
+  </si>
+  <si>
+    <t>Still monolithic by design, not ideal for ultra‑light microservices</t>
+  </si>
+  <si>
+    <t>Latest major release focusing on minimalism, performance, and modern PHP architecture.</t>
+  </si>
+  <si>
+    <t>Symfony 3.4.49</t>
+  </si>
+  <si>
+    <t>LTS improvements; better caching; enhanced DI container</t>
+  </si>
+  <si>
+    <t>Outdated architecture; lacks modern PHP features</t>
+  </si>
+  <si>
+    <t>Symfony Core Team</t>
+  </si>
+  <si>
+    <t>LTS release widely used in legacy enterprise systems</t>
+  </si>
+  <si>
+    <t>Symfony 4.4.51</t>
+  </si>
+  <si>
+    <t>Improved Flex; better Messenger; enhanced HTTP client</t>
+  </si>
+  <si>
+    <t>Limited async support; older PHP compatibility</t>
+  </si>
+  <si>
+    <t>Modern LTS release powering many enterprise apps</t>
+  </si>
+  <si>
+    <t>Symfony 5.4.40</t>
+  </si>
+  <si>
+    <t>Improved Messenger; HttpClient; Mailer; better DX</t>
+  </si>
+  <si>
+    <t>Still monolithic for microservices; heavy for small apps</t>
+  </si>
+  <si>
+    <t>Stable LTS release with strong performance and tooling</t>
+  </si>
+  <si>
+    <t>Symfony 6.4.8</t>
+  </si>
+  <si>
+    <t>PHP 8.2 support; improved serializer; better routing; enhanced security</t>
+  </si>
+  <si>
+    <t>Complex for beginners; requires strong conventions</t>
+  </si>
+  <si>
+    <t>Modern LTS release focused on performance and DX</t>
+  </si>
+  <si>
+    <t>Symfony 7.1.2</t>
+  </si>
+  <si>
+    <t>PHP 8.3 support; improved HttpKernel; async improvements; better caching</t>
+  </si>
+  <si>
+    <t>Still opinionated and enterprise‑heavy</t>
+  </si>
+  <si>
+    <t>Latest stable release with major performance and async improvements</t>
+  </si>
+  <si>
+    <t>2021-01-01</t>
+  </si>
+  <si>
+    <t>2022-11-30</t>
+  </si>
+  <si>
+    <t>2023-01-01</t>
+  </si>
+  <si>
+    <t>2023-11-30</t>
+  </si>
+  <si>
+    <t>2025-11-30</t>
+  </si>
+  <si>
+    <t>2024-12-10</t>
+  </si>
+  <si>
+    <t>2028-11-30</t>
+  </si>
+  <si>
+    <t>2025-03-20</t>
+  </si>
+  <si>
+    <t>2030-11-30</t>
   </si>
 </sst>
 </file>
@@ -3493,19 +4705,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}">
-  <dimension ref="A1:L371"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L368"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.88671875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="28.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="28.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="28.140625" customWidth="1"/>
+    <col min="12" max="12" width="28.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3543,7 +4755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -3581,7 +4793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
@@ -3619,7 +4831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
@@ -3657,7 +4869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
@@ -3695,7 +4907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
@@ -3733,7 +4945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>53</v>
       </c>
@@ -3771,7 +4983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
@@ -3809,7 +5021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>67</v>
       </c>
@@ -3847,7 +5059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -3885,7 +5097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>80</v>
       </c>
@@ -3921,7 +5133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>87</v>
       </c>
@@ -3959,7 +5171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>95</v>
       </c>
@@ -3997,7 +5209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>101</v>
       </c>
@@ -4035,7 +5247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>107</v>
       </c>
@@ -4073,7 +5285,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>113</v>
       </c>
@@ -4111,7 +5323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>120</v>
       </c>
@@ -4149,7 +5361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>126</v>
       </c>
@@ -4187,7 +5399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>133</v>
       </c>
@@ -4225,7 +5437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>140</v>
       </c>
@@ -4263,7 +5475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>146</v>
       </c>
@@ -4301,7 +5513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>152</v>
       </c>
@@ -4339,7 +5551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>159</v>
       </c>
@@ -4375,7 +5587,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>170</v>
       </c>
@@ -4411,7 +5623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>171</v>
       </c>
@@ -4447,7 +5659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>176</v>
       </c>
@@ -4483,7 +5695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>181</v>
       </c>
@@ -4519,7 +5731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>186</v>
       </c>
@@ -4555,7 +5767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>192</v>
       </c>
@@ -4591,7 +5803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>197</v>
       </c>
@@ -4627,7 +5839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>202</v>
       </c>
@@ -4663,7 +5875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>207</v>
       </c>
@@ -4699,7 +5911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>208</v>
       </c>
@@ -4735,7 +5947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>209</v>
       </c>
@@ -4771,7 +5983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>221</v>
       </c>
@@ -4807,7 +6019,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>226</v>
       </c>
@@ -4843,7 +6055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>231</v>
       </c>
@@ -4879,7 +6091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>236</v>
       </c>
@@ -4915,7 +6127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>243</v>
       </c>
@@ -4951,7 +6163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>249</v>
       </c>
@@ -4987,7 +6199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>254</v>
       </c>
@@ -5025,7 +6237,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>261</v>
       </c>
@@ -5063,7 +6275,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>267</v>
       </c>
@@ -5101,7 +6313,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>273</v>
       </c>
@@ -5139,7 +6351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>279</v>
       </c>
@@ -5177,7 +6389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>284</v>
       </c>
@@ -5215,7 +6427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>289</v>
       </c>
@@ -5253,7 +6465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>295</v>
       </c>
@@ -5291,7 +6503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>301</v>
       </c>
@@ -5327,7 +6539,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>307</v>
       </c>
@@ -5363,7 +6575,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>312</v>
       </c>
@@ -5399,7 +6611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>318</v>
       </c>
@@ -5435,7 +6647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>321</v>
       </c>
@@ -5471,7 +6683,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>326</v>
       </c>
@@ -5507,7 +6719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>331</v>
       </c>
@@ -5543,7 +6755,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>336</v>
       </c>
@@ -5579,7 +6791,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>340</v>
       </c>
@@ -5615,7 +6827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>346</v>
       </c>
@@ -5651,7 +6863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>351</v>
       </c>
@@ -5687,7 +6899,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>356</v>
       </c>
@@ -5723,7 +6935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>361</v>
       </c>
@@ -5759,7 +6971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>366</v>
       </c>
@@ -5795,7 +7007,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>371</v>
       </c>
@@ -5831,7 +7043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>376</v>
       </c>
@@ -5867,7 +7079,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>380</v>
       </c>
@@ -5903,7 +7115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>386</v>
       </c>
@@ -5939,7 +7151,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>391</v>
       </c>
@@ -5975,7 +7187,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>396</v>
       </c>
@@ -6011,7 +7223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>402</v>
       </c>
@@ -6047,7 +7259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>403</v>
       </c>
@@ -6083,7 +7295,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>404</v>
       </c>
@@ -6119,7 +7331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>405</v>
       </c>
@@ -6155,7 +7367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>420</v>
       </c>
@@ -6193,7 +7405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>427</v>
       </c>
@@ -6231,7 +7443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>433</v>
       </c>
@@ -6269,7 +7481,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>439</v>
       </c>
@@ -6307,7 +7519,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>445</v>
       </c>
@@ -6345,7 +7557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>451</v>
       </c>
@@ -6383,7 +7595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>452</v>
       </c>
@@ -6421,7 +7633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>462</v>
       </c>
@@ -6459,7 +7671,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>469</v>
       </c>
@@ -6497,7 +7709,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>475</v>
       </c>
@@ -6535,7 +7747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>481</v>
       </c>
@@ -6573,7 +7785,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>487</v>
       </c>
@@ -6609,7 +7821,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="s">
         <v>493</v>
       </c>
@@ -6645,7 +7857,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>498</v>
       </c>
@@ -6681,7 +7893,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>503</v>
       </c>
@@ -6717,7 +7929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>509</v>
       </c>
@@ -6753,7 +7965,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>515</v>
       </c>
@@ -6789,7 +8001,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>520</v>
       </c>
@@ -6825,7 +8037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>525</v>
       </c>
@@ -6861,7 +8073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>531</v>
       </c>
@@ -6897,7 +8109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>536</v>
       </c>
@@ -6933,7 +8145,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>541</v>
       </c>
@@ -6969,7 +8181,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>545</v>
       </c>
@@ -7005,7 +8217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>552</v>
       </c>
@@ -7041,7 +8253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>558</v>
       </c>
@@ -7077,7 +8289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>563</v>
       </c>
@@ -7113,7 +8325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>568</v>
       </c>
@@ -7149,7 +8361,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>573</v>
       </c>
@@ -7185,7 +8397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>579</v>
       </c>
@@ -7221,7 +8433,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>584</v>
       </c>
@@ -7257,7 +8469,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>589</v>
       </c>
@@ -7293,7 +8505,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="13" t="s">
         <v>594</v>
       </c>
@@ -7329,7 +8541,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="29.4" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9" t="s">
         <v>606</v>
       </c>
@@ -7367,7 +8579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A106" s="9" t="s">
         <v>612</v>
       </c>
@@ -7405,7 +8617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>618</v>
       </c>
@@ -7443,7 +8655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>624</v>
       </c>
@@ -7481,7 +8693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>630</v>
       </c>
@@ -7519,7 +8731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A110" s="9" t="s">
         <v>599</v>
       </c>
@@ -7557,7 +8769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" s="9" t="s">
         <v>636</v>
       </c>
@@ -7595,7 +8807,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>667</v>
       </c>
@@ -7633,7 +8845,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>678</v>
       </c>
@@ -7671,7 +8883,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>688</v>
       </c>
@@ -7709,7 +8921,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>698</v>
       </c>
@@ -7747,7 +8959,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>708</v>
       </c>
@@ -7785,7 +8997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>719</v>
       </c>
@@ -7823,7 +9035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>729</v>
       </c>
@@ -7861,7 +9073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>739</v>
       </c>
@@ -7899,7 +9111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>747</v>
       </c>
@@ -7937,7 +9149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>755</v>
       </c>
@@ -7975,7 +9187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>764</v>
       </c>
@@ -8013,7 +9225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>774</v>
       </c>
@@ -8051,7 +9263,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>783</v>
       </c>
@@ -8089,7 +9301,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>791</v>
       </c>
@@ -8127,7 +9339,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>800</v>
       </c>
@@ -8165,7 +9377,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>809</v>
       </c>
@@ -8203,7 +9415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>818</v>
       </c>
@@ -8241,7 +9453,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>825</v>
       </c>
@@ -8279,7 +9491,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>832</v>
       </c>
@@ -8317,7 +9529,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>840</v>
       </c>
@@ -8355,7 +9567,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>850</v>
       </c>
@@ -8393,7 +9605,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>859</v>
       </c>
@@ -8431,7 +9643,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>865</v>
       </c>
@@ -8469,7 +9681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>874</v>
       </c>
@@ -8507,194 +9719,218 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="198" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="3"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="3"/>
-    </row>
-    <row r="137" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>885</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="G136" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="H136" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="I136" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="J136" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="K136" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="L136" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>885</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>886</v>
-      </c>
+        <v>896</v>
+      </c>
+      <c r="E137" s="5"/>
       <c r="F137" s="5" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="G137" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="I137" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="H137" s="4" t="s">
+      <c r="J137" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="I137" s="4" t="s">
-        <v>890</v>
-      </c>
-      <c r="J137" s="4" t="s">
-        <v>891</v>
-      </c>
       <c r="K137" s="5" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="L137" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="135" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>894</v>
+        <v>901</v>
+      </c>
+      <c r="B138" s="16" t="s">
+        <v>902</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>896</v>
-      </c>
-      <c r="E138" s="5"/>
+        <v>904</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>905</v>
+      </c>
       <c r="F138" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="5">
+        <v>75</v>
+      </c>
+      <c r="H138" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="H138" s="4" t="s">
+      <c r="I138" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="I138" s="4" t="s">
+      <c r="J138" s="4" t="s">
         <v>888</v>
       </c>
-      <c r="J138" s="4" t="s">
-        <v>889</v>
-      </c>
       <c r="K138" s="5" t="s">
-        <v>900</v>
+        <v>906</v>
       </c>
       <c r="L138" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>902</v>
+        <v>907</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>908</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>904</v>
+        <v>909</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>905</v>
+        <v>911</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>897</v>
       </c>
-      <c r="G139" s="5">
-        <v>75</v>
+      <c r="G139" s="4" t="s">
+        <v>912</v>
       </c>
       <c r="H139" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I139" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="I139" s="4" t="s">
+      <c r="J139" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="J139" s="4" t="s">
-        <v>888</v>
-      </c>
       <c r="K139" s="5" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="L139" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>908</v>
+        <v>372</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>897</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>898</v>
+        <v>921</v>
       </c>
       <c r="J140" s="4" t="s">
-        <v>899</v>
+        <v>922</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="L140" s="3">
         <v>22</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>915</v>
+        <v>924</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>372</v>
+        <v>925</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>916</v>
+        <v>926</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>917</v>
+        <v>927</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>897</v>
+        <v>929</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="I141" s="4" t="s">
         <v>921</v>
@@ -8703,1547 +9939,3315 @@
         <v>922</v>
       </c>
       <c r="K141" s="5" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="L141" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>929</v>
       </c>
       <c r="G142" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I142" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J142" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="H142" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="I142" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="J142" s="4" t="s">
-        <v>922</v>
-      </c>
       <c r="K142" s="5" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="L142" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>931</v>
+        <v>937</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>933</v>
+        <v>903</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>934</v>
+        <v>939</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>935</v>
+        <v>940</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>929</v>
       </c>
       <c r="G143" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J143" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="H143" s="4" t="s">
-        <v>920</v>
-      </c>
-      <c r="I143" s="4" t="s">
-        <v>899</v>
-      </c>
-      <c r="J143" s="4" t="s">
-        <v>898</v>
-      </c>
       <c r="K143" s="5" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="L143" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>937</v>
+        <v>943</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>939</v>
+        <v>945</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>929</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>941</v>
+        <v>912</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>912</v>
+        <v>947</v>
       </c>
       <c r="I144" s="4" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="J144" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="L144" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>944</v>
+        <v>526</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>910</v>
+        <v>950</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>929</v>
       </c>
       <c r="G145" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J145" s="4" t="s">
         <v>912</v>
       </c>
-      <c r="H145" s="4" t="s">
-        <v>947</v>
-      </c>
-      <c r="I145" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="J145" s="4" t="s">
-        <v>920</v>
-      </c>
       <c r="K145" s="5" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="L145" s="3">
         <v>23</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>526</v>
+        <v>956</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>929</v>
+        <v>131</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>919</v>
+        <v>898</v>
       </c>
       <c r="H146" s="4" t="s">
-        <v>953</v>
+        <v>913</v>
       </c>
       <c r="I146" s="4" t="s">
-        <v>920</v>
+        <v>899</v>
       </c>
       <c r="J146" s="4" t="s">
-        <v>912</v>
+        <v>888</v>
       </c>
       <c r="K146" s="5" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="L146" s="3">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>958</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>959</v>
-      </c>
+        <v>964</v>
+      </c>
+      <c r="E147" s="5"/>
       <c r="F147" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G147" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I147" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="H147" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="I147" s="4" t="s">
+      <c r="J147" s="4" t="s">
         <v>899</v>
       </c>
-      <c r="J147" s="4" t="s">
-        <v>888</v>
-      </c>
       <c r="K147" s="5" t="s">
-        <v>960</v>
+        <v>965</v>
       </c>
       <c r="L147" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>961</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>962</v>
+        <v>966</v>
+      </c>
+      <c r="B148" s="16" t="s">
+        <v>967</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>963</v>
+        <v>128</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>964</v>
-      </c>
-      <c r="E148" s="5"/>
+        <v>968</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>969</v>
+      </c>
       <c r="F148" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G148" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I148" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="H148" s="4" t="s">
-        <v>912</v>
-      </c>
-      <c r="I148" s="4" t="s">
+      <c r="J148" s="4" t="s">
         <v>898</v>
       </c>
-      <c r="J148" s="4" t="s">
-        <v>899</v>
-      </c>
       <c r="K148" s="5" t="s">
-        <v>965</v>
+        <v>970</v>
       </c>
       <c r="L148" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="B149" s="16" t="s">
-        <v>967</v>
+        <v>971</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>128</v>
+        <v>972</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>968</v>
+        <v>973</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>969</v>
+        <v>974</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H149" s="4" t="s">
-        <v>947</v>
+        <v>975</v>
       </c>
       <c r="I149" s="4" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="J149" s="4" t="s">
-        <v>898</v>
+        <v>921</v>
       </c>
       <c r="K149" s="5" t="s">
-        <v>970</v>
+        <v>976</v>
       </c>
       <c r="L149" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>971</v>
+        <v>977</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>972</v>
+        <v>978</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>973</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>974</v>
-      </c>
+        <v>979</v>
+      </c>
+      <c r="E150" s="5"/>
       <c r="F150" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>919</v>
+        <v>953</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>975</v>
+        <v>980</v>
       </c>
       <c r="I150" s="4" t="s">
-        <v>920</v>
+        <v>947</v>
       </c>
       <c r="J150" s="4" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="K150" s="5" t="s">
-        <v>976</v>
+        <v>981</v>
       </c>
       <c r="L150" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>977</v>
+        <v>982</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>978</v>
+        <v>983</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>979</v>
-      </c>
-      <c r="E151" s="5"/>
+        <v>984</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>985</v>
+      </c>
       <c r="F151" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G151" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I151" s="4" t="s">
         <v>953</v>
       </c>
-      <c r="H151" s="4" t="s">
-        <v>980</v>
-      </c>
-      <c r="I151" s="4" t="s">
-        <v>947</v>
-      </c>
       <c r="J151" s="4" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="K151" s="5" t="s">
-        <v>981</v>
+        <v>987</v>
       </c>
       <c r="L151" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>982</v>
+        <v>988</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>984</v>
+        <v>990</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>985</v>
+        <v>991</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>131</v>
       </c>
       <c r="G152" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H152" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I152" s="4" t="s">
         <v>980</v>
       </c>
-      <c r="H152" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="I152" s="4" t="s">
-        <v>953</v>
-      </c>
       <c r="J152" s="4" t="s">
-        <v>919</v>
+        <v>947</v>
       </c>
       <c r="K152" s="5" t="s">
-        <v>987</v>
+        <v>993</v>
       </c>
       <c r="L152" s="3">
         <v>24</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>153</v>
+        <v>995</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>131</v>
+        <v>999</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>986</v>
+        <v>889</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>992</v>
+        <v>888</v>
       </c>
       <c r="I153" s="4" t="s">
-        <v>980</v>
+        <v>891</v>
       </c>
       <c r="J153" s="4" t="s">
-        <v>947</v>
+        <v>1000</v>
       </c>
       <c r="K153" s="5" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="L153" s="3">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="59.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>999</v>
       </c>
       <c r="G154" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I154" s="4" t="s">
         <v>889</v>
       </c>
-      <c r="H154" s="4" t="s">
-        <v>888</v>
-      </c>
-      <c r="I154" s="4" t="s">
-        <v>891</v>
-      </c>
       <c r="J154" s="4" t="s">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>1001</v>
+        <v>1007</v>
       </c>
       <c r="L154" s="3">
         <v>25</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>1003</v>
+        <v>1009</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>1004</v>
+        <v>1010</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E155" s="5"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="4"/>
-      <c r="H155" s="4"/>
-      <c r="I155" s="4"/>
-      <c r="J155" s="4"/>
-      <c r="K155" s="5"/>
-      <c r="L155" s="3"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A156" s="3"/>
-      <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
-      <c r="D156" s="5"/>
-      <c r="E156" s="5"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="4"/>
-      <c r="H156" s="4"/>
-      <c r="I156" s="4"/>
-      <c r="J156" s="4"/>
-      <c r="K156" s="5"/>
-      <c r="L156" s="3"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A157" s="3"/>
-      <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
-      <c r="D157" s="5"/>
-      <c r="E157" s="5"/>
-      <c r="F157" s="5"/>
-      <c r="G157" s="4"/>
-      <c r="H157" s="4"/>
-      <c r="I157" s="4"/>
-      <c r="J157" s="4"/>
-      <c r="K157" s="5"/>
-      <c r="L157" s="3"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="3"/>
-      <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
-      <c r="D158" s="5"/>
-      <c r="E158" s="5"/>
-      <c r="F158" s="5"/>
-      <c r="G158" s="4"/>
-      <c r="H158" s="4"/>
-      <c r="I158" s="4"/>
-      <c r="J158" s="4"/>
-      <c r="K158" s="5"/>
-      <c r="L158" s="3"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A159" s="3"/>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="5"/>
-      <c r="E159" s="5"/>
-      <c r="F159" s="5"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
-      <c r="K159" s="5"/>
-      <c r="L159" s="3"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A160" s="3"/>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="5"/>
-      <c r="E160" s="5"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="5"/>
-      <c r="L160" s="3"/>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A161" s="3"/>
-      <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
-      <c r="D161" s="5"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="5"/>
-      <c r="G161" s="4"/>
-      <c r="H161" s="4"/>
-      <c r="I161" s="4"/>
-      <c r="J161" s="4"/>
-      <c r="K161" s="5"/>
-      <c r="L161" s="3"/>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A162" s="3"/>
-      <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
-      <c r="D162" s="5"/>
-      <c r="E162" s="5"/>
-      <c r="F162" s="5"/>
-      <c r="G162" s="4"/>
-      <c r="H162" s="4"/>
-      <c r="I162" s="4"/>
-      <c r="J162" s="4"/>
-      <c r="K162" s="5"/>
-      <c r="L162" s="3"/>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A163" s="3"/>
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="5"/>
-      <c r="E163" s="5"/>
-      <c r="F163" s="5"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
-      <c r="I163" s="4"/>
-      <c r="J163" s="4"/>
-      <c r="K163" s="5"/>
-      <c r="L163" s="3"/>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A164" s="3"/>
-      <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
-      <c r="F164" s="5"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="4"/>
-      <c r="J164" s="4"/>
-      <c r="K164" s="5"/>
-      <c r="L164" s="3"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A165" s="3"/>
-      <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="5"/>
-      <c r="E165" s="5"/>
-      <c r="F165" s="5"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="4"/>
-      <c r="J165" s="4"/>
-      <c r="K165" s="5"/>
-      <c r="L165" s="3"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A166" s="3"/>
-      <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="5"/>
-      <c r="E166" s="5"/>
-      <c r="F166" s="5"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="4"/>
-      <c r="J166" s="4"/>
-      <c r="K166" s="5"/>
-      <c r="L166" s="3"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A167" s="3"/>
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="5"/>
-      <c r="E167" s="5"/>
-      <c r="F167" s="5"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="4"/>
-      <c r="J167" s="4"/>
-      <c r="K167" s="5"/>
-      <c r="L167" s="3"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A168" s="3"/>
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="5"/>
-      <c r="E168" s="5"/>
-      <c r="F168" s="5"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="4"/>
-      <c r="J168" s="4"/>
-      <c r="K168" s="5"/>
-      <c r="L168" s="3"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A169" s="3"/>
-      <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="5"/>
-      <c r="E169" s="5"/>
-      <c r="F169" s="5"/>
-      <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
-      <c r="I169" s="4"/>
-      <c r="J169" s="4"/>
-      <c r="K169" s="5"/>
-      <c r="L169" s="3"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A170" s="3"/>
-      <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="5"/>
-      <c r="E170" s="5"/>
-      <c r="F170" s="5"/>
-      <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="4"/>
-      <c r="J170" s="4"/>
-      <c r="K170" s="5"/>
-      <c r="L170" s="3"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A171" s="3"/>
-      <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="5"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="4"/>
-      <c r="J171" s="4"/>
-      <c r="K171" s="5"/>
-      <c r="L171" s="3"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A172" s="3"/>
-      <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="5"/>
-      <c r="E172" s="5"/>
-      <c r="F172" s="5"/>
-      <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
-      <c r="I172" s="4"/>
-      <c r="J172" s="4"/>
-      <c r="K172" s="5"/>
-      <c r="L172" s="3"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A173" s="3"/>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="5"/>
-      <c r="E173" s="5"/>
-      <c r="F173" s="5"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-      <c r="I173" s="4"/>
-      <c r="J173" s="4"/>
-      <c r="K173" s="5"/>
-      <c r="L173" s="3"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A174" s="3"/>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="5"/>
-      <c r="F174" s="5"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="4"/>
-      <c r="J174" s="4"/>
-      <c r="K174" s="5"/>
-      <c r="L174" s="3"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A175" s="3"/>
-      <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="5"/>
-      <c r="F175" s="5"/>
-      <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
-      <c r="I175" s="4"/>
-      <c r="J175" s="4"/>
-      <c r="K175" s="5"/>
-      <c r="L175" s="3"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A176" s="3"/>
-      <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="5"/>
-      <c r="E176" s="5"/>
-      <c r="F176" s="5"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="4"/>
-      <c r="J176" s="4"/>
-      <c r="K176" s="5"/>
-      <c r="L176" s="3"/>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A177" s="3"/>
-      <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="5"/>
-      <c r="E177" s="5"/>
-      <c r="F177" s="5"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="4"/>
-      <c r="J177" s="4"/>
-      <c r="K177" s="5"/>
-      <c r="L177" s="3"/>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A178" s="3"/>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="5"/>
-      <c r="E178" s="5"/>
-      <c r="F178" s="5"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="4"/>
-      <c r="J178" s="4"/>
-      <c r="K178" s="5"/>
-      <c r="L178" s="3"/>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A179" s="3"/>
-      <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="5"/>
-      <c r="E179" s="5"/>
-      <c r="F179" s="5"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-      <c r="I179" s="4"/>
-      <c r="J179" s="4"/>
-      <c r="K179" s="5"/>
-      <c r="L179" s="3"/>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A180" s="3"/>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="5"/>
-      <c r="E180" s="5"/>
-      <c r="F180" s="5"/>
-      <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="4"/>
-      <c r="J180" s="4"/>
-      <c r="K180" s="5"/>
-      <c r="L180" s="3"/>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A181" s="3"/>
-      <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="5"/>
-      <c r="E181" s="5"/>
-      <c r="F181" s="5"/>
-      <c r="G181" s="4"/>
-      <c r="H181" s="4"/>
-      <c r="I181" s="4"/>
-      <c r="J181" s="4"/>
-      <c r="K181" s="5"/>
-      <c r="L181" s="3"/>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" s="3"/>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="5"/>
-      <c r="E182" s="5"/>
-      <c r="F182" s="5"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
-      <c r="I182" s="4"/>
-      <c r="J182" s="4"/>
-      <c r="K182" s="5"/>
-      <c r="L182" s="3"/>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" s="3"/>
-      <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
-      <c r="D183" s="5"/>
-      <c r="E183" s="5"/>
-      <c r="F183" s="5"/>
-      <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
-      <c r="I183" s="4"/>
-      <c r="J183" s="4"/>
-      <c r="K183" s="5"/>
-      <c r="L183" s="3"/>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" s="3"/>
-      <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
-      <c r="D184" s="5"/>
-      <c r="E184" s="5"/>
-      <c r="F184" s="5"/>
-      <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
-      <c r="I184" s="4"/>
-      <c r="J184" s="4"/>
-      <c r="K184" s="5"/>
-      <c r="L184" s="3"/>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" s="3"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
-      <c r="D185" s="5"/>
-      <c r="E185" s="5"/>
-      <c r="F185" s="5"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="4"/>
-      <c r="J185" s="4"/>
-      <c r="K185" s="5"/>
-      <c r="L185" s="3"/>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" s="3"/>
-      <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
-      <c r="D186" s="5"/>
-      <c r="E186" s="5"/>
-      <c r="F186" s="5"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="4"/>
-      <c r="J186" s="4"/>
-      <c r="K186" s="5"/>
-      <c r="L186" s="3"/>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" s="3"/>
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
-      <c r="D187" s="5"/>
-      <c r="E187" s="5"/>
-      <c r="F187" s="5"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-      <c r="I187" s="4"/>
-      <c r="J187" s="4"/>
-      <c r="K187" s="5"/>
-      <c r="L187" s="3"/>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" s="3"/>
-      <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
-      <c r="D188" s="5"/>
-      <c r="E188" s="5"/>
-      <c r="F188" s="5"/>
-      <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="4"/>
-      <c r="J188" s="4"/>
-      <c r="K188" s="5"/>
-      <c r="L188" s="3"/>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" s="3"/>
-      <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
-      <c r="D189" s="5"/>
-      <c r="E189" s="5"/>
-      <c r="F189" s="5"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="4"/>
-      <c r="J189" s="4"/>
-      <c r="K189" s="5"/>
-      <c r="L189" s="3"/>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" s="3"/>
-      <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
-      <c r="D190" s="5"/>
-      <c r="E190" s="5"/>
-      <c r="F190" s="5"/>
-      <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="4"/>
-      <c r="J190" s="4"/>
-      <c r="K190" s="5"/>
-      <c r="L190" s="3"/>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" s="3"/>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="5"/>
-      <c r="E191" s="5"/>
-      <c r="F191" s="5"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="4"/>
-      <c r="J191" s="4"/>
-      <c r="K191" s="5"/>
-      <c r="L191" s="3"/>
-    </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A192" s="3"/>
-      <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
-      <c r="D192" s="5"/>
-      <c r="E192" s="5"/>
-      <c r="F192" s="5"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="4"/>
-      <c r="J192" s="4"/>
-      <c r="K192" s="5"/>
-      <c r="L192" s="3"/>
-    </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A193" s="3"/>
-      <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
-      <c r="D193" s="5"/>
-      <c r="E193" s="5"/>
-      <c r="F193" s="5"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-      <c r="I193" s="4"/>
-      <c r="J193" s="4"/>
-      <c r="K193" s="5"/>
-      <c r="L193" s="3"/>
-    </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A194" s="3"/>
-      <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
-      <c r="D194" s="5"/>
-      <c r="E194" s="5"/>
-      <c r="F194" s="5"/>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="4"/>
-      <c r="J194" s="4"/>
-      <c r="K194" s="5"/>
-      <c r="L194" s="3"/>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A195" s="3"/>
-      <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="5"/>
-      <c r="E195" s="5"/>
-      <c r="F195" s="5"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
-      <c r="K195" s="5"/>
-      <c r="L195" s="3"/>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A196" s="3"/>
-      <c r="B196" s="4"/>
-      <c r="C196" s="4"/>
-      <c r="D196" s="5"/>
-      <c r="E196" s="5"/>
-      <c r="F196" s="5"/>
-      <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="4"/>
-      <c r="J196" s="4"/>
-      <c r="K196" s="5"/>
-      <c r="L196" s="3"/>
-    </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A197" s="3"/>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="5"/>
-      <c r="E197" s="5"/>
-      <c r="F197" s="5"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-      <c r="I197" s="4"/>
-      <c r="J197" s="4"/>
-      <c r="K197" s="5"/>
-      <c r="L197" s="3"/>
-    </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A198" s="3"/>
-      <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
-      <c r="D198" s="5"/>
-      <c r="E198" s="5"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
-      <c r="I198" s="4"/>
-      <c r="J198" s="4"/>
-      <c r="K198" s="5"/>
-      <c r="L198" s="3"/>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A199" s="3"/>
-      <c r="B199" s="4"/>
-      <c r="C199" s="4"/>
-      <c r="D199" s="5"/>
-      <c r="E199" s="5"/>
-      <c r="F199" s="5"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
-      <c r="I199" s="4"/>
-      <c r="J199" s="4"/>
-      <c r="K199" s="5"/>
-      <c r="L199" s="3"/>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A200" s="3"/>
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="5"/>
-      <c r="E200" s="5"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="4"/>
-      <c r="J200" s="4"/>
-      <c r="K200" s="5"/>
-      <c r="L200" s="3"/>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A201" s="3"/>
-      <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="5"/>
-      <c r="E201" s="5"/>
-      <c r="F201" s="5"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="4"/>
-      <c r="J201" s="4"/>
-      <c r="K201" s="5"/>
-      <c r="L201" s="3"/>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A202" s="3"/>
-      <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="5"/>
-      <c r="E202" s="5"/>
-      <c r="F202" s="5"/>
-      <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
-      <c r="I202" s="4"/>
-      <c r="J202" s="4"/>
-      <c r="K202" s="5"/>
-      <c r="L202" s="3"/>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A203" s="3"/>
-      <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="4"/>
-      <c r="H203" s="4"/>
-      <c r="I203" s="4"/>
-      <c r="J203" s="4"/>
-      <c r="K203" s="5"/>
-      <c r="L203" s="3"/>
-    </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A204" s="3"/>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="5"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
-      <c r="I204" s="4"/>
-      <c r="J204" s="4"/>
-      <c r="K204" s="5"/>
-      <c r="L204" s="3"/>
-    </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A205" s="3"/>
-      <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
-      <c r="D205" s="5"/>
-      <c r="E205" s="5"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
-      <c r="I205" s="4"/>
-      <c r="J205" s="4"/>
-      <c r="K205" s="5"/>
-      <c r="L205" s="3"/>
-    </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A206" s="3"/>
-      <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="5"/>
-      <c r="E206" s="5"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
-      <c r="I206" s="4"/>
-      <c r="J206" s="4"/>
-      <c r="K206" s="5"/>
-      <c r="L206" s="3"/>
-    </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A207" s="3"/>
-      <c r="B207" s="4"/>
-      <c r="C207" s="4"/>
-      <c r="D207" s="5"/>
-      <c r="E207" s="5"/>
-      <c r="F207" s="5"/>
-      <c r="G207" s="4"/>
-      <c r="H207" s="4"/>
-      <c r="I207" s="4"/>
-      <c r="J207" s="4"/>
-      <c r="K207" s="5"/>
-      <c r="L207" s="3"/>
-    </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A208" s="3"/>
-      <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="5"/>
-      <c r="E208" s="5"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
-      <c r="I208" s="4"/>
-      <c r="J208" s="4"/>
-      <c r="K208" s="5"/>
-      <c r="L208" s="3"/>
-    </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A209" s="3"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="5"/>
-      <c r="E209" s="5"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
-      <c r="I209" s="4"/>
-      <c r="J209" s="4"/>
-      <c r="K209" s="5"/>
-      <c r="L209" s="3"/>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A210" s="3"/>
-      <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
-      <c r="D210" s="5"/>
-      <c r="E210" s="5"/>
-      <c r="F210" s="5"/>
-      <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
-      <c r="I210" s="4"/>
-      <c r="J210" s="4"/>
-      <c r="K210" s="5"/>
-      <c r="L210" s="3"/>
-    </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A211" s="3"/>
-      <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="5"/>
-      <c r="E211" s="5"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
-      <c r="I211" s="4"/>
-      <c r="J211" s="4"/>
-      <c r="K211" s="5"/>
-      <c r="L211" s="3"/>
-    </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A212" s="3"/>
-      <c r="B212" s="4"/>
-      <c r="C212" s="4"/>
-      <c r="D212" s="5"/>
-      <c r="E212" s="5"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="4"/>
-      <c r="H212" s="4"/>
-      <c r="I212" s="4"/>
-      <c r="J212" s="4"/>
-      <c r="K212" s="5"/>
-      <c r="L212" s="3"/>
-    </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A213" s="3"/>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="5"/>
-      <c r="E213" s="5"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="4"/>
-      <c r="H213" s="4"/>
-      <c r="I213" s="4"/>
-      <c r="J213" s="4"/>
-      <c r="K213" s="5"/>
-      <c r="L213" s="3"/>
-    </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A214" s="3"/>
-      <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
-      <c r="D214" s="5"/>
-      <c r="E214" s="5"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
-      <c r="I214" s="4"/>
-      <c r="J214" s="4"/>
-      <c r="K214" s="5"/>
-      <c r="L214" s="3"/>
-    </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A215" s="3"/>
-      <c r="B215" s="4"/>
-      <c r="C215" s="4"/>
-      <c r="D215" s="5"/>
-      <c r="E215" s="5"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="4"/>
-      <c r="H215" s="4"/>
-      <c r="I215" s="4"/>
-      <c r="J215" s="4"/>
-      <c r="K215" s="5"/>
-      <c r="L215" s="3"/>
-    </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A216" s="3"/>
-      <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
-      <c r="D216" s="5"/>
-      <c r="E216" s="5"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
-      <c r="I216" s="4"/>
-      <c r="J216" s="4"/>
-      <c r="K216" s="5"/>
-      <c r="L216" s="3"/>
-    </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A217" s="3"/>
-      <c r="B217" s="4"/>
-      <c r="C217" s="4"/>
-      <c r="D217" s="5"/>
-      <c r="E217" s="5"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="4"/>
-      <c r="I217" s="4"/>
-      <c r="J217" s="4"/>
-      <c r="K217" s="5"/>
-      <c r="L217" s="3"/>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A218" s="3"/>
-      <c r="B218" s="4"/>
-      <c r="C218" s="4"/>
-      <c r="D218" s="5"/>
-      <c r="E218" s="5"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="4"/>
-      <c r="I218" s="4"/>
-      <c r="J218" s="4"/>
-      <c r="K218" s="5"/>
-      <c r="L218" s="3"/>
-    </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A219" s="3"/>
-      <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
-      <c r="D219" s="5"/>
-      <c r="E219" s="5"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="4"/>
-      <c r="H219" s="4"/>
-      <c r="I219" s="4"/>
-      <c r="J219" s="4"/>
-      <c r="K219" s="5"/>
-      <c r="L219" s="3"/>
-    </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A220" s="3"/>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="5"/>
-      <c r="E220" s="5"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="4"/>
-      <c r="H220" s="4"/>
-      <c r="I220" s="4"/>
-      <c r="J220" s="4"/>
-      <c r="K220" s="5"/>
-      <c r="L220" s="3"/>
-    </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A221" s="3"/>
-      <c r="B221" s="4"/>
-      <c r="C221" s="4"/>
-      <c r="D221" s="5"/>
-      <c r="E221" s="5"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="4"/>
-      <c r="H221" s="4"/>
-      <c r="I221" s="4"/>
-      <c r="J221" s="4"/>
-      <c r="K221" s="5"/>
-      <c r="L221" s="3"/>
-    </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A222" s="3"/>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="5"/>
-      <c r="E222" s="5"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="4"/>
-      <c r="J222" s="4"/>
-      <c r="K222" s="5"/>
-      <c r="L222" s="3"/>
-    </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A223" s="3"/>
-      <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
-      <c r="D223" s="5"/>
-      <c r="E223" s="5"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
-      <c r="I223" s="4"/>
-      <c r="J223" s="4"/>
-      <c r="K223" s="5"/>
-      <c r="L223" s="3"/>
-    </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A224" s="3"/>
-      <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
-      <c r="D224" s="5"/>
-      <c r="E224" s="5"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="4"/>
-      <c r="H224" s="4"/>
-      <c r="I224" s="4"/>
-      <c r="J224" s="4"/>
-      <c r="K224" s="5"/>
-      <c r="L224" s="3"/>
-    </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A225" s="3"/>
-      <c r="B225" s="4"/>
-      <c r="C225" s="4"/>
-      <c r="D225" s="5"/>
-      <c r="E225" s="5"/>
-      <c r="F225" s="5"/>
-      <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
-      <c r="I225" s="4"/>
-      <c r="J225" s="4"/>
-      <c r="K225" s="5"/>
-      <c r="L225" s="3"/>
-    </row>
-    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A226" s="3"/>
-      <c r="B226" s="4"/>
-      <c r="C226" s="4"/>
-      <c r="D226" s="5"/>
-      <c r="E226" s="5"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
-      <c r="I226" s="4"/>
-      <c r="J226" s="4"/>
-      <c r="K226" s="5"/>
-      <c r="L226" s="3"/>
-    </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A227" s="3"/>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="5"/>
-      <c r="E227" s="5"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
-      <c r="I227" s="4"/>
-      <c r="J227" s="4"/>
-      <c r="K227" s="5"/>
-      <c r="L227" s="3"/>
-    </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A228" s="3"/>
-      <c r="B228" s="4"/>
-      <c r="C228" s="4"/>
-      <c r="D228" s="5"/>
-      <c r="E228" s="5"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
-      <c r="I228" s="4"/>
-      <c r="J228" s="4"/>
-      <c r="K228" s="5"/>
-      <c r="L228" s="3"/>
-    </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1011</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I155" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J155" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K155" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L155" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="G156" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="H156" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I156" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J156" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K156" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L156" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A157" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I157" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J157" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="K157" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L157" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G158" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H158" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I158" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="J158" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K158" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L158" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A159" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G159" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H159" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I159" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J159" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K159" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="L159" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="H160" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I160" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="J160" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="K160" s="5" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L160" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A161" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G161" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H161" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I161" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J161" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K161" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L161" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G162" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H162" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I162" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J162" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="K162" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="L162" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A163" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G163" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H163" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I163" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="J163" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K163" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="L163" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G164" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H164" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I164" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J164" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K164" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L164" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A165" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G165" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I165" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J165" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K165" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="L165" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G166" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I166" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J166" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="K166" s="5" t="s">
+        <v>1089</v>
+      </c>
+      <c r="L166" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H167" s="4" t="s">
+        <v>1063</v>
+      </c>
+      <c r="I167" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="J167" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="K167" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="L167" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H168" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I168" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="J168" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K168" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L168" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A169" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H169" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I169" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J169" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K169" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L169" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H170" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I170" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="J170" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K170" s="5" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L170" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A171" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H171" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I171" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J171" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K171" s="5" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L171" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G172" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="H172" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="I172" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="J172" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="K172" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L172" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A173" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G173" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="H173" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I173" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="J173" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K173" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L173" s="3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G174" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H174" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="I174" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J174" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K174" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L174" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A175" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="H175" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I175" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="J175" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K175" s="5" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L175" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H176" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I176" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J176" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K176" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="L176" s="3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A177" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H177" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I177" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J177" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K177" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="L177" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G178" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H178" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I178" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J178" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K178" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="L178" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A179" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H179" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I179" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J179" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="K179" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="L179" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H180" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I180" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J180" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K180" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L180" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A181" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G181" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H181" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I181" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="J181" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="K181" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L181" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G182" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H182" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I182" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="J182" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="K182" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L182" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A183" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G183" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H183" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I183" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J183" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K183" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="L183" s="3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="H184" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I184" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="J184" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K184" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="L184" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A185" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E185" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I185" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J185" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K185" s="5" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L185" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E186" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="I186" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="J186" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="K186" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L186" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A187" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G187" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="H187" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="I187" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="J187" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K187" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="L187" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H188" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="I188" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J188" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="K188" s="5" t="s">
+        <v>1213</v>
+      </c>
+      <c r="L188" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A189" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="E189" s="5" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="H189" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I189" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="J189" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K189" s="5" t="s">
+        <v>1218</v>
+      </c>
+      <c r="L189" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E190" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G190" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H190" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I190" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J190" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="K190" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="L190" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A191" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G191" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H191" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I191" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="J191" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K191" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L191" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>1231</v>
+      </c>
+      <c r="E192" s="5" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="G192" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="H192" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="I192" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J192" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K192" s="5" t="s">
+        <v>1233</v>
+      </c>
+      <c r="L192" s="3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A193" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>1237</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H193" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I193" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J193" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K193" s="5" t="s">
+        <v>1239</v>
+      </c>
+      <c r="L193" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E194" s="5" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I194" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J194" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K194" s="5" t="s">
+        <v>1244</v>
+      </c>
+      <c r="L194" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A195" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E195" s="5" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>1238</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J195" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K195" s="5" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L195" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E196" s="5" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G196" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H196" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I196" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J196" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K196" s="5" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L196" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A197" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E197" s="5" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I197" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J197" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K197" s="5" t="s">
+        <v>1259</v>
+      </c>
+      <c r="L197" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I198" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J198" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K198" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L198" s="3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A199" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G199" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="H199" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I199" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J199" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K199" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L199" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G200" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H200" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I200" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="J200" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="K200" s="5" t="s">
+        <v>1275</v>
+      </c>
+      <c r="L200" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A201" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G201" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H201" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I201" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J201" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="K201" s="5" t="s">
+        <v>1280</v>
+      </c>
+      <c r="L201" s="3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I202" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J202" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K202" s="5" t="s">
+        <v>1286</v>
+      </c>
+      <c r="L202" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A203" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I203" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J203" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K203" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="L203" s="3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A204" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="H204" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="I204" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="J204" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="K204" s="5" t="s">
+        <v>1298</v>
+      </c>
+      <c r="L204" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A205" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>1297</v>
+      </c>
+      <c r="G205" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H205" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="I205" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J205" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>1302</v>
+      </c>
+      <c r="L205" s="3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H206" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I206" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J206" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K206" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L206" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A207" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H207" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I207" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J207" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K207" s="5" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L207" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G208" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H208" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I208" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J208" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K208" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L208" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A209" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="G209" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H209" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="I209" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J209" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K209" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L209" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G210" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H210" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I210" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="J210" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="K210" s="5" t="s">
+        <v>1330</v>
+      </c>
+      <c r="L210" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A211" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H211" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="I211" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="J211" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="K211" s="5" t="s">
+        <v>1335</v>
+      </c>
+      <c r="L211" s="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C212" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="H212" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="I212" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="J212" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="K212" s="5" t="s">
+        <v>1342</v>
+      </c>
+      <c r="L212" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A213" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C213" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G213" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H213" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I213" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J213" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K213" s="5" t="s">
+        <v>1348</v>
+      </c>
+      <c r="L213" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>1351</v>
+      </c>
+      <c r="E214" s="5" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="H214" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="I214" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="J214" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="K214" s="5" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L214" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A215" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E215" s="5" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H215" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I215" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J215" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K215" s="5" t="s">
+        <v>1359</v>
+      </c>
+      <c r="L215" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="H216" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="I216" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="J216" s="4" t="s">
+        <v>1365</v>
+      </c>
+      <c r="K216" s="5" t="s">
+        <v>1366</v>
+      </c>
+      <c r="L216" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>1369</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H217" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I217" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J217" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K217" s="5" t="s">
+        <v>1372</v>
+      </c>
+      <c r="L217" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" ht="72" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H218" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I218" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J218" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K218" s="5" t="s">
+        <v>1378</v>
+      </c>
+      <c r="L218" s="3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G219" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H219" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I219" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J219" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K219" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L219" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G220" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H220" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I220" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J220" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K220" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="L220" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A221" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H221" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I221" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J221" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K221" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L221" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H222" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I222" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J222" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K222" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L222" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A223" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G223" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H223" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I223" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J223" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K223" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L223" s="3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>1381</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="H224" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I224" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="J224" s="4" t="s">
+        <v>1141</v>
+      </c>
+      <c r="K224" s="5" t="s">
+        <v>1383</v>
+      </c>
+      <c r="L224" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G225" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="H225" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="I225" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="J225" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="K225" s="5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="L225" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="H226" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="I226" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="J226" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="K226" s="5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="L226" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>1394</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="H227" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I227" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="J227" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="K227" s="5" t="s">
+        <v>1395</v>
+      </c>
+      <c r="L227" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>1382</v>
+      </c>
+      <c r="G228" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H228" s="4" t="s">
+        <v>1069</v>
+      </c>
+      <c r="I228" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="J228" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K228" s="5" t="s">
+        <v>1399</v>
+      </c>
+      <c r="L228" s="3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -10257,7 +13261,7 @@
       <c r="K229" s="5"/>
       <c r="L229" s="3"/>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -10271,7 +13275,7 @@
       <c r="K230" s="5"/>
       <c r="L230" s="3"/>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -10285,7 +13289,7 @@
       <c r="K231" s="5"/>
       <c r="L231" s="3"/>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -10299,7 +13303,7 @@
       <c r="K232" s="5"/>
       <c r="L232" s="3"/>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -10313,7 +13317,7 @@
       <c r="K233" s="5"/>
       <c r="L233" s="3"/>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -10327,7 +13331,7 @@
       <c r="K234" s="5"/>
       <c r="L234" s="3"/>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -10341,7 +13345,7 @@
       <c r="K235" s="5"/>
       <c r="L235" s="3"/>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -10355,7 +13359,7 @@
       <c r="K236" s="5"/>
       <c r="L236" s="3"/>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -10369,7 +13373,7 @@
       <c r="K237" s="5"/>
       <c r="L237" s="3"/>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -10383,7 +13387,7 @@
       <c r="K238" s="5"/>
       <c r="L238" s="3"/>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="3"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -10397,7 +13401,7 @@
       <c r="K239" s="5"/>
       <c r="L239" s="3"/>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -10411,7 +13415,7 @@
       <c r="K240" s="5"/>
       <c r="L240" s="3"/>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -10425,7 +13429,7 @@
       <c r="K241" s="5"/>
       <c r="L241" s="3"/>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="3"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -10439,7 +13443,7 @@
       <c r="K242" s="5"/>
       <c r="L242" s="3"/>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="3"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -10453,7 +13457,7 @@
       <c r="K243" s="5"/>
       <c r="L243" s="3"/>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -10467,7 +13471,7 @@
       <c r="K244" s="5"/>
       <c r="L244" s="3"/>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -10481,7 +13485,7 @@
       <c r="K245" s="5"/>
       <c r="L245" s="3"/>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -10495,7 +13499,7 @@
       <c r="K246" s="5"/>
       <c r="L246" s="3"/>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -10509,7 +13513,7 @@
       <c r="K247" s="5"/>
       <c r="L247" s="3"/>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -10523,7 +13527,7 @@
       <c r="K248" s="5"/>
       <c r="L248" s="3"/>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -10537,7 +13541,7 @@
       <c r="K249" s="5"/>
       <c r="L249" s="3"/>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -10551,7 +13555,7 @@
       <c r="K250" s="5"/>
       <c r="L250" s="3"/>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -10565,7 +13569,7 @@
       <c r="K251" s="5"/>
       <c r="L251" s="3"/>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -10579,7 +13583,7 @@
       <c r="K252" s="5"/>
       <c r="L252" s="3"/>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -10593,7 +13597,7 @@
       <c r="K253" s="5"/>
       <c r="L253" s="3"/>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -10607,7 +13611,7 @@
       <c r="K254" s="5"/>
       <c r="L254" s="3"/>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -10621,7 +13625,7 @@
       <c r="K255" s="5"/>
       <c r="L255" s="3"/>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -10635,7 +13639,7 @@
       <c r="K256" s="5"/>
       <c r="L256" s="3"/>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -10649,7 +13653,7 @@
       <c r="K257" s="5"/>
       <c r="L257" s="3"/>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -10663,7 +13667,7 @@
       <c r="K258" s="5"/>
       <c r="L258" s="3"/>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -10677,7 +13681,7 @@
       <c r="K259" s="5"/>
       <c r="L259" s="3"/>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -10691,7 +13695,7 @@
       <c r="K260" s="5"/>
       <c r="L260" s="3"/>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="3"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -10705,7 +13709,7 @@
       <c r="K261" s="5"/>
       <c r="L261" s="3"/>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -10719,7 +13723,7 @@
       <c r="K262" s="5"/>
       <c r="L262" s="3"/>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="3"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -10733,7 +13737,7 @@
       <c r="K263" s="5"/>
       <c r="L263" s="3"/>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="3"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -10747,7 +13751,7 @@
       <c r="K264" s="5"/>
       <c r="L264" s="3"/>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="3"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -10761,7 +13765,7 @@
       <c r="K265" s="5"/>
       <c r="L265" s="3"/>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" s="3"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -10775,7 +13779,7 @@
       <c r="K266" s="5"/>
       <c r="L266" s="3"/>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="3"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -10789,7 +13793,7 @@
       <c r="K267" s="5"/>
       <c r="L267" s="3"/>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="3"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -10803,7 +13807,7 @@
       <c r="K268" s="5"/>
       <c r="L268" s="3"/>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="3"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -10817,7 +13821,7 @@
       <c r="K269" s="5"/>
       <c r="L269" s="3"/>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="3"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -10831,7 +13835,7 @@
       <c r="K270" s="5"/>
       <c r="L270" s="3"/>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="3"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -10845,7 +13849,7 @@
       <c r="K271" s="5"/>
       <c r="L271" s="3"/>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="3"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -10859,7 +13863,7 @@
       <c r="K272" s="5"/>
       <c r="L272" s="3"/>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="3"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -10873,7 +13877,7 @@
       <c r="K273" s="5"/>
       <c r="L273" s="3"/>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="3"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -10887,7 +13891,7 @@
       <c r="K274" s="5"/>
       <c r="L274" s="3"/>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="3"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -10901,7 +13905,7 @@
       <c r="K275" s="5"/>
       <c r="L275" s="3"/>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="3"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -10915,7 +13919,7 @@
       <c r="K276" s="5"/>
       <c r="L276" s="3"/>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="3"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -10929,7 +13933,7 @@
       <c r="K277" s="5"/>
       <c r="L277" s="3"/>
     </row>
-    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="3"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -10943,7 +13947,7 @@
       <c r="K278" s="5"/>
       <c r="L278" s="3"/>
     </row>
-    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="3"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -10957,7 +13961,7 @@
       <c r="K279" s="5"/>
       <c r="L279" s="3"/>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="3"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -10971,7 +13975,7 @@
       <c r="K280" s="5"/>
       <c r="L280" s="3"/>
     </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="3"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -10985,7 +13989,7 @@
       <c r="K281" s="5"/>
       <c r="L281" s="3"/>
     </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="3"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -10999,7 +14003,7 @@
       <c r="K282" s="5"/>
       <c r="L282" s="3"/>
     </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="3"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -11013,7 +14017,7 @@
       <c r="K283" s="5"/>
       <c r="L283" s="3"/>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="3"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -11027,7 +14031,7 @@
       <c r="K284" s="5"/>
       <c r="L284" s="3"/>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="3"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -11041,7 +14045,7 @@
       <c r="K285" s="5"/>
       <c r="L285" s="3"/>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="3"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -11055,7 +14059,7 @@
       <c r="K286" s="5"/>
       <c r="L286" s="3"/>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="3"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -11069,7 +14073,7 @@
       <c r="K287" s="5"/>
       <c r="L287" s="3"/>
     </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="3"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -11083,7 +14087,7 @@
       <c r="K288" s="5"/>
       <c r="L288" s="3"/>
     </row>
-    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="3"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -11097,7 +14101,7 @@
       <c r="K289" s="5"/>
       <c r="L289" s="3"/>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -11111,7 +14115,7 @@
       <c r="K290" s="5"/>
       <c r="L290" s="3"/>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -11125,7 +14129,7 @@
       <c r="K291" s="5"/>
       <c r="L291" s="3"/>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="3"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -11139,7 +14143,7 @@
       <c r="K292" s="5"/>
       <c r="L292" s="3"/>
     </row>
-    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="3"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -11153,7 +14157,7 @@
       <c r="K293" s="5"/>
       <c r="L293" s="3"/>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="3"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -11167,7 +14171,7 @@
       <c r="K294" s="5"/>
       <c r="L294" s="3"/>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="3"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -11181,7 +14185,7 @@
       <c r="K295" s="5"/>
       <c r="L295" s="3"/>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="3"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -11195,7 +14199,7 @@
       <c r="K296" s="5"/>
       <c r="L296" s="3"/>
     </row>
-    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="3"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -11209,7 +14213,7 @@
       <c r="K297" s="5"/>
       <c r="L297" s="3"/>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="3"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -11223,7 +14227,7 @@
       <c r="K298" s="5"/>
       <c r="L298" s="3"/>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="3"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -11237,7 +14241,7 @@
       <c r="K299" s="5"/>
       <c r="L299" s="3"/>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="3"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -11251,7 +14255,7 @@
       <c r="K300" s="5"/>
       <c r="L300" s="3"/>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="3"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -11265,7 +14269,7 @@
       <c r="K301" s="5"/>
       <c r="L301" s="3"/>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="3"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -11279,7 +14283,7 @@
       <c r="K302" s="5"/>
       <c r="L302" s="3"/>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="3"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -11293,7 +14297,7 @@
       <c r="K303" s="5"/>
       <c r="L303" s="3"/>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="3"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -11307,7 +14311,7 @@
       <c r="K304" s="5"/>
       <c r="L304" s="3"/>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="3"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -11321,7 +14325,7 @@
       <c r="K305" s="5"/>
       <c r="L305" s="3"/>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="3"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -11335,7 +14339,7 @@
       <c r="K306" s="5"/>
       <c r="L306" s="3"/>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="3"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -11349,7 +14353,7 @@
       <c r="K307" s="5"/>
       <c r="L307" s="3"/>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="3"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -11363,7 +14367,7 @@
       <c r="K308" s="5"/>
       <c r="L308" s="3"/>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="3"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -11377,7 +14381,7 @@
       <c r="K309" s="5"/>
       <c r="L309" s="3"/>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="3"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -11391,7 +14395,7 @@
       <c r="K310" s="5"/>
       <c r="L310" s="3"/>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="3"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -11405,7 +14409,7 @@
       <c r="K311" s="5"/>
       <c r="L311" s="3"/>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="3"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -11419,7 +14423,7 @@
       <c r="K312" s="5"/>
       <c r="L312" s="3"/>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="3"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -11433,7 +14437,7 @@
       <c r="K313" s="5"/>
       <c r="L313" s="3"/>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="3"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -11447,7 +14451,7 @@
       <c r="K314" s="5"/>
       <c r="L314" s="3"/>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="3"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -11461,7 +14465,7 @@
       <c r="K315" s="5"/>
       <c r="L315" s="3"/>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="3"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -11475,7 +14479,7 @@
       <c r="K316" s="5"/>
       <c r="L316" s="3"/>
     </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="3"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -11489,7 +14493,7 @@
       <c r="K317" s="5"/>
       <c r="L317" s="3"/>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="3"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -11503,7 +14507,7 @@
       <c r="K318" s="5"/>
       <c r="L318" s="3"/>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="3"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -11517,7 +14521,7 @@
       <c r="K319" s="5"/>
       <c r="L319" s="3"/>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="3"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -11531,7 +14535,7 @@
       <c r="K320" s="5"/>
       <c r="L320" s="3"/>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="3"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -11545,7 +14549,7 @@
       <c r="K321" s="5"/>
       <c r="L321" s="3"/>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="3"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -11559,7 +14563,7 @@
       <c r="K322" s="5"/>
       <c r="L322" s="3"/>
     </row>
-    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="3"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -11573,7 +14577,7 @@
       <c r="K323" s="5"/>
       <c r="L323" s="3"/>
     </row>
-    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="3"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -11587,7 +14591,7 @@
       <c r="K324" s="5"/>
       <c r="L324" s="3"/>
     </row>
-    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="3"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -11601,7 +14605,7 @@
       <c r="K325" s="5"/>
       <c r="L325" s="3"/>
     </row>
-    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="3"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -11615,7 +14619,7 @@
       <c r="K326" s="5"/>
       <c r="L326" s="3"/>
     </row>
-    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="3"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -11629,7 +14633,7 @@
       <c r="K327" s="5"/>
       <c r="L327" s="3"/>
     </row>
-    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="3"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -11643,7 +14647,7 @@
       <c r="K328" s="5"/>
       <c r="L328" s="3"/>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="3"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -11657,7 +14661,7 @@
       <c r="K329" s="5"/>
       <c r="L329" s="3"/>
     </row>
-    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="3"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -11671,7 +14675,7 @@
       <c r="K330" s="5"/>
       <c r="L330" s="3"/>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="3"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -11685,7 +14689,7 @@
       <c r="K331" s="5"/>
       <c r="L331" s="3"/>
     </row>
-    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="3"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -11699,7 +14703,7 @@
       <c r="K332" s="5"/>
       <c r="L332" s="3"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="3"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -11713,7 +14717,7 @@
       <c r="K333" s="5"/>
       <c r="L333" s="3"/>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="3"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -11727,7 +14731,7 @@
       <c r="K334" s="5"/>
       <c r="L334" s="3"/>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="3"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -11741,7 +14745,7 @@
       <c r="K335" s="5"/>
       <c r="L335" s="3"/>
     </row>
-    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="3"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -11755,7 +14759,7 @@
       <c r="K336" s="5"/>
       <c r="L336" s="3"/>
     </row>
-    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="3"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -11769,7 +14773,7 @@
       <c r="K337" s="5"/>
       <c r="L337" s="3"/>
     </row>
-    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A338" s="3"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -11783,7 +14787,7 @@
       <c r="K338" s="5"/>
       <c r="L338" s="3"/>
     </row>
-    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="3"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -11797,7 +14801,7 @@
       <c r="K339" s="5"/>
       <c r="L339" s="3"/>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="3"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -11811,7 +14815,7 @@
       <c r="K340" s="5"/>
       <c r="L340" s="3"/>
     </row>
-    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="3"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -11825,7 +14829,7 @@
       <c r="K341" s="5"/>
       <c r="L341" s="3"/>
     </row>
-    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="3"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -11839,7 +14843,7 @@
       <c r="K342" s="5"/>
       <c r="L342" s="3"/>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="3"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -11853,7 +14857,7 @@
       <c r="K343" s="5"/>
       <c r="L343" s="3"/>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="3"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -11867,7 +14871,7 @@
       <c r="K344" s="5"/>
       <c r="L344" s="3"/>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="3"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -11881,7 +14885,7 @@
       <c r="K345" s="5"/>
       <c r="L345" s="3"/>
     </row>
-    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="3"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -11895,7 +14899,7 @@
       <c r="K346" s="5"/>
       <c r="L346" s="3"/>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="3"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -11909,7 +14913,7 @@
       <c r="K347" s="5"/>
       <c r="L347" s="3"/>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="3"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -11923,7 +14927,7 @@
       <c r="K348" s="5"/>
       <c r="L348" s="3"/>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="3"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -11937,7 +14941,7 @@
       <c r="K349" s="5"/>
       <c r="L349" s="3"/>
     </row>
-    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="3"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -11951,7 +14955,7 @@
       <c r="K350" s="5"/>
       <c r="L350" s="3"/>
     </row>
-    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="3"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -11965,7 +14969,7 @@
       <c r="K351" s="5"/>
       <c r="L351" s="3"/>
     </row>
-    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="3"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -11979,7 +14983,7 @@
       <c r="K352" s="5"/>
       <c r="L352" s="3"/>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="3"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -11993,7 +14997,7 @@
       <c r="K353" s="5"/>
       <c r="L353" s="3"/>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="3"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -12007,7 +15011,7 @@
       <c r="K354" s="5"/>
       <c r="L354" s="3"/>
     </row>
-    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="3"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -12021,7 +15025,7 @@
       <c r="K355" s="5"/>
       <c r="L355" s="3"/>
     </row>
-    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="3"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -12035,7 +15039,7 @@
       <c r="K356" s="5"/>
       <c r="L356" s="3"/>
     </row>
-    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="3"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -12049,7 +15053,7 @@
       <c r="K357" s="5"/>
       <c r="L357" s="3"/>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="3"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -12063,7 +15067,7 @@
       <c r="K358" s="5"/>
       <c r="L358" s="3"/>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="3"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -12077,7 +15081,7 @@
       <c r="K359" s="5"/>
       <c r="L359" s="3"/>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="3"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -12091,7 +15095,7 @@
       <c r="K360" s="5"/>
       <c r="L360" s="3"/>
     </row>
-    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="3"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -12105,7 +15109,7 @@
       <c r="K361" s="5"/>
       <c r="L361" s="3"/>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="3"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -12119,7 +15123,7 @@
       <c r="K362" s="5"/>
       <c r="L362" s="3"/>
     </row>
-    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="3"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -12133,7 +15137,7 @@
       <c r="K363" s="5"/>
       <c r="L363" s="3"/>
     </row>
-    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="3"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -12147,7 +15151,7 @@
       <c r="K364" s="5"/>
       <c r="L364" s="3"/>
     </row>
-    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="3"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -12161,7 +15165,7 @@
       <c r="K365" s="5"/>
       <c r="L365" s="3"/>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="3"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -12175,7 +15179,7 @@
       <c r="K366" s="5"/>
       <c r="L366" s="3"/>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="3"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -12189,7 +15193,7 @@
       <c r="K367" s="5"/>
       <c r="L367" s="3"/>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="3"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -12203,48 +15207,6 @@
       <c r="K368" s="5"/>
       <c r="L368" s="3"/>
     </row>
-    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A369" s="3"/>
-      <c r="B369" s="4"/>
-      <c r="C369" s="4"/>
-      <c r="D369" s="5"/>
-      <c r="E369" s="5"/>
-      <c r="F369" s="5"/>
-      <c r="G369" s="4"/>
-      <c r="H369" s="4"/>
-      <c r="I369" s="4"/>
-      <c r="J369" s="4"/>
-      <c r="K369" s="5"/>
-      <c r="L369" s="3"/>
-    </row>
-    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A370" s="3"/>
-      <c r="B370" s="4"/>
-      <c r="C370" s="4"/>
-      <c r="D370" s="5"/>
-      <c r="E370" s="5"/>
-      <c r="F370" s="5"/>
-      <c r="G370" s="4"/>
-      <c r="H370" s="4"/>
-      <c r="I370" s="4"/>
-      <c r="J370" s="4"/>
-      <c r="K370" s="5"/>
-      <c r="L370" s="3"/>
-    </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A371" s="3"/>
-      <c r="B371" s="4"/>
-      <c r="C371" s="4"/>
-      <c r="D371" s="5"/>
-      <c r="E371" s="5"/>
-      <c r="F371" s="5"/>
-      <c r="G371" s="4"/>
-      <c r="H371" s="4"/>
-      <c r="I371" s="4"/>
-      <c r="J371" s="4"/>
-      <c r="K371" s="5"/>
-      <c r="L371" s="3"/>
-    </row>
   </sheetData>
   <autoFilter ref="A1:L2" xr:uid="{41043218-9C94-410C-9ADE-FF0FB1887CD8}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
